--- a/05_Figures/F06_prediction/proteins/trajectory/d_fcsa_II/spls/c_data/results.xlsx
+++ b/05_Figures/F06_prediction/proteins/trajectory/d_fcsa_II/spls/c_data/results.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="187" uniqueCount="187">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="177" uniqueCount="177">
   <si>
     <t xml:space="preserve">level</t>
   </si>
@@ -134,46 +134,64 @@
     <t xml:space="preserve">PPP1R2@T3</t>
   </si>
   <si>
+    <t xml:space="preserve">SEC23A@T2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EIF3F@T2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LYPLA2@T1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MRPS18B@T3</t>
+  </si>
+  <si>
     <t xml:space="preserve">PSMB5@T3</t>
   </si>
   <si>
-    <t xml:space="preserve">SEC23A@T2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EIF3F@T2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LYPLA2@T1</t>
+    <t xml:space="preserve">RPL17@T3</t>
   </si>
   <si>
     <t xml:space="preserve">TMEM11@T1</t>
   </si>
   <si>
+    <t xml:space="preserve">VPS13C@T1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BPNT1@T3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SLC25A3@T3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SLC44A2@T2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ZYX@T1</t>
+  </si>
+  <si>
     <t xml:space="preserve">MAP2K2@T3</t>
   </si>
   <si>
-    <t xml:space="preserve">RPL17@T3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BPNT1@T3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MRPS18B@T3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SLC25A3@T3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">VPS13C@T1</t>
+    <t xml:space="preserve">CAMK2A@T2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LDHB@T2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MYH3@T3</t>
   </si>
   <si>
     <t xml:space="preserve">TGM2@T3</t>
   </si>
   <si>
+    <t xml:space="preserve">ASPH@T2</t>
+  </si>
+  <si>
     <t xml:space="preserve">ATP6V1H@T1</t>
   </si>
   <si>
-    <t xml:space="preserve">CAMK2A@T2</t>
+    <t xml:space="preserve">CRIP2@T2</t>
   </si>
   <si>
     <t xml:space="preserve">LAMTOR3@T1</t>
@@ -182,10 +200,7 @@
     <t xml:space="preserve">PDIA4@T2</t>
   </si>
   <si>
-    <t xml:space="preserve">ZYX@T1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ASPH@T2</t>
+    <t xml:space="preserve">DYNC1I2@T3</t>
   </si>
   <si>
     <t xml:space="preserve">FSCN1@T2</t>
@@ -194,379 +209,334 @@
     <t xml:space="preserve">HDHD2@T1</t>
   </si>
   <si>
-    <t xml:space="preserve">LDHB@T2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MYH3@T3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SLC44A2@T2</t>
+    <t xml:space="preserve">METAP2@T1</t>
   </si>
   <si>
     <t xml:space="preserve">TUBB2A@T2</t>
   </si>
   <si>
-    <t xml:space="preserve">CRIP2@T2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DYNC1I2@T3</t>
+    <t xml:space="preserve">ECHDC3@T1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HADHA@T2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ATP5F1E@T1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CACNG1@T2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CAMK2G@T1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DCTN2@T2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GLUL@T3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GPX1@T3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HK1@T3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NGLY1@T2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PURA@T3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RPL23A@T2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AK1@T3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BLVRA@T3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CCDC43@T3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DUSP3@T2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GORASP2@T3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HLA-A@T2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LUM@T1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MPO@T1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MRPS27@T2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NAPRT@T3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PSME3@T3</t>
   </si>
   <si>
     <t xml:space="preserve">RAB1A@T1</t>
   </si>
   <si>
-    <t xml:space="preserve">CACNG1@T2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GPX1@T3</t>
+    <t xml:space="preserve">SDHD@T1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SUMO2@T2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TTC38@T2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ACADSB@T1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ACADVL@T2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AIMP1@T2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AIMP2@T2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AK1@T1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AK1@T2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ANXA11@T3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ANXA3@T3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ARMT1@T1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ARPP19@T2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ASS1@T3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ATP2A3@T2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CACNB3@T2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CAND1@T1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CAPZA2@T3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CASQ1@T1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CD59@T3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CLIP1@T3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CRIP1@T2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CUL2@T1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DCAF8@T3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DCXR@T3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DHRS11@T3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DHRS7B@T2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DPYSL3@T2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DYNLRB1@T3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EIF2S3@T2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EIF3G@T1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EIF3G@T2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EIF3L@T2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EIF5B@T2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EPB41L2@T1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ESYT1@T2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FARSB@T2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FARSB@T3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FECH@T3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FHOD1@T2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FUNDC2@T1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GLO1@T3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GMPR@T2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GPX1@T1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HK1@T2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HNRNPC@T3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HSD17B4@T1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">KARS1@T1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MAN2C1@T3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MAP3K20@T3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MBNL1@T3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">METAP2@T2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MGLL@T3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MRPL22@T2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MT-ND1@T1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MYBPC2@T2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NAGK@T2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NARS1@T3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NT5C2@T3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OGDH@T2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PCBP2@T2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PMPCB@T3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PPID@T3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PPM1A@T3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PRUNE1@T1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PSAPL1@T2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">QARS1@T1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RAB8A@T2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RPA3@T3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RPL12@T3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RPL13A@T3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RPL7@T3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RPL7A@T3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RUVBL2@T1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SCRN3@T3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SDHC@T1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SFXN1@T3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SGTA@T2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SH3BGRL3@T1</t>
   </si>
   <si>
     <t xml:space="preserve">SNX5@T2</t>
   </si>
   <si>
-    <t xml:space="preserve">CAMK2G@T1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DCTN2@T2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DUSP3@T2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ECHDC3@T1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GLUL@T3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HK1@T3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">METAP2@T1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NGLY1@T2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RPL23A@T2</t>
-  </si>
-  <si>
     <t xml:space="preserve">SRSF2@T1</t>
   </si>
   <si>
-    <t xml:space="preserve">AK1@T3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ATP5F1E@T1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HADHA@T2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SDHD@T1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SUMO2@T2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TTC38@T2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ARPP19@T2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ATP2A3@T2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BLVRA@T3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CCDC43@T3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">COX20@T1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DHRS7B@T2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FARSB@T2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HK1@T2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HLA-A@T2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LUM@T1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MFAP4@T1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MRPS27@T2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NAPRT@T3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PURA@T3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SFXN1@T3</t>
+    <t xml:space="preserve">TMEM43@T3</t>
   </si>
   <si>
     <t xml:space="preserve">TMX4@T3</t>
   </si>
   <si>
-    <t xml:space="preserve">ACADSB@T1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ACADVL@T2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AIMP1@T2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AIMP2@T2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AK1@T1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AK1@T2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ANXA11@T3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ANXA3@T3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ARMT1@T1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ATP5MF@T3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CACNB3@T2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CAND1@T1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CAPZA2@T3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CASQ1@T1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CD59@T3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CDNF@T3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CLIP1@T3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CRIP1@T2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CUL2@T1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DCXR@T3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DPYSL3@T2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DYNLRB1@T3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EIF2S3@T2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EIF3G@T1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EIF3G@T2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EIF3L@T2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EIF5B@T2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EIF5B@T3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ENDOD1@T2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EPB41L2@T1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ESYT1@T2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FARSB@T3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FECH@T3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FHOD1@T2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FUNDC2@T1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GLO1@T3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GMPR@T2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GPX1@T1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HLA-DRA@T3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HNRNPC@T3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HSD17B12@T2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HSD17B4@T1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">KARS1@T1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MAN2C1@T3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MAP3K20@T3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MBNL1@T3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">METAP2@T2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MGLL@T3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MRPL22@T2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MT-ND1@T1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MYBPC2@T2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MYH1@T2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NAGK@T2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NARS1@T3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NT5C2@T3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">OGDH@T2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PCBP2@T2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PDCD6IP@T3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PMPCB@T3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PRUNE1@T1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PSAPL1@T2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PSMA2@T3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">QARS1@T1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RAB11B@T2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RAB8A@T2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RBMX@T3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RPA3@T3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RPL12@T3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RPL13A@T3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RPL17@T2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RPL7@T3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RPL7A@T3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RUVBL2@T1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RUVBL2@T2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SCRN3@T3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SDHC@T1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SGTA@T2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SH3BGRL3@T1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SPPL2A@T1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">STOM@T2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TMEM43@T3</t>
-  </si>
-  <si>
     <t xml:space="preserve">TXNDC17@T1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">UBE2M@T2</t>
   </si>
   <si>
     <t xml:space="preserve">WDR1@T2</t>
@@ -962,16 +932,16 @@
         <v>14</v>
       </c>
       <c r="F2" t="n">
-        <v>5711</v>
+        <v>5696</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
       </c>
       <c r="H2" t="n">
-        <v>-0.15703458011933</v>
+        <v>-0.131188602948822</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.0593406593406593</v>
+        <v>0.103296703296703</v>
       </c>
       <c r="J2"/>
       <c r="K2"/>
@@ -995,29 +965,21 @@
         <v>14</v>
       </c>
       <c r="F3" t="n">
-        <v>5711</v>
+        <v>5696</v>
       </c>
       <c r="G3" t="n">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.15703458011933</v>
+        <v>-0.131188602948822</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.0593406593406593</v>
-      </c>
-      <c r="J3" t="n">
-        <v>0.253731343283582</v>
-      </c>
-      <c r="K3" t="n">
-        <v>0.393034825870647</v>
-      </c>
-      <c r="L3" t="n">
-        <v>-0.613378629036752</v>
-      </c>
-      <c r="M3" t="n">
-        <v>0.59567467701827</v>
-      </c>
+        <v>0.103296703296703</v>
+      </c>
+      <c r="J3"/>
+      <c r="K3"/>
+      <c r="L3"/>
+      <c r="M3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1041,2206 +1003,6 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="s">
-        <v>15</v>
-      </c>
-      <c r="B2" t="s">
-        <v>16</v>
-      </c>
-      <c r="C2" t="n">
-        <v>-1.37656781754147</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="s">
-        <v>15</v>
-      </c>
-      <c r="B3" t="s">
-        <v>16</v>
-      </c>
-      <c r="C3" t="n">
-        <v>-1.79267396404171</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="s">
-        <v>15</v>
-      </c>
-      <c r="B4" t="s">
-        <v>16</v>
-      </c>
-      <c r="C4" t="n">
-        <v>-1.12241523497539</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="s">
-        <v>15</v>
-      </c>
-      <c r="B5" t="s">
-        <v>16</v>
-      </c>
-      <c r="C5" t="n">
-        <v>-1.33844750058831</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="s">
-        <v>15</v>
-      </c>
-      <c r="B6" t="s">
-        <v>16</v>
-      </c>
-      <c r="C6" t="n">
-        <v>-0.581009399975765</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="s">
-        <v>15</v>
-      </c>
-      <c r="B7" t="s">
-        <v>16</v>
-      </c>
-      <c r="C7" t="n">
-        <v>-0.493606826755245</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="s">
-        <v>15</v>
-      </c>
-      <c r="B8" t="s">
-        <v>16</v>
-      </c>
-      <c r="C8" t="n">
-        <v>-0.0497505251473473</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="s">
-        <v>15</v>
-      </c>
-      <c r="B9" t="s">
-        <v>16</v>
-      </c>
-      <c r="C9" t="n">
-        <v>0.551969586008467</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="s">
-        <v>15</v>
-      </c>
-      <c r="B10" t="s">
-        <v>16</v>
-      </c>
-      <c r="C10" t="n">
-        <v>-0.646938126600557</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="s">
-        <v>15</v>
-      </c>
-      <c r="B11" t="s">
-        <v>16</v>
-      </c>
-      <c r="C11" t="n">
-        <v>-1.33530143966052</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="s">
-        <v>15</v>
-      </c>
-      <c r="B12" t="s">
-        <v>16</v>
-      </c>
-      <c r="C12" t="n">
-        <v>-0.279334966988617</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="s">
-        <v>15</v>
-      </c>
-      <c r="B13" t="s">
-        <v>16</v>
-      </c>
-      <c r="C13" t="n">
-        <v>-0.533249781458115</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="s">
-        <v>15</v>
-      </c>
-      <c r="B14" t="s">
-        <v>16</v>
-      </c>
-      <c r="C14" t="n">
-        <v>-0.978300871086647</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="s">
-        <v>15</v>
-      </c>
-      <c r="B15" t="s">
-        <v>16</v>
-      </c>
-      <c r="C15" t="n">
-        <v>0.0891454412149196</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="s">
-        <v>15</v>
-      </c>
-      <c r="B16" t="s">
-        <v>16</v>
-      </c>
-      <c r="C16" t="n">
-        <v>-0.0223547881593964</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="s">
-        <v>15</v>
-      </c>
-      <c r="B17" t="s">
-        <v>16</v>
-      </c>
-      <c r="C17" t="n">
-        <v>0.149379472575172</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="s">
-        <v>15</v>
-      </c>
-      <c r="B18" t="s">
-        <v>16</v>
-      </c>
-      <c r="C18" t="n">
-        <v>-0.123514300000002</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="s">
-        <v>15</v>
-      </c>
-      <c r="B19" t="s">
-        <v>16</v>
-      </c>
-      <c r="C19" t="n">
-        <v>-0.452993317899693</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="s">
-        <v>15</v>
-      </c>
-      <c r="B20" t="s">
-        <v>16</v>
-      </c>
-      <c r="C20" t="n">
-        <v>-0.499491804789987</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="s">
-        <v>15</v>
-      </c>
-      <c r="B21" t="s">
-        <v>16</v>
-      </c>
-      <c r="C21" t="n">
-        <v>-0.442581031980583</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="s">
-        <v>15</v>
-      </c>
-      <c r="B22" t="s">
-        <v>16</v>
-      </c>
-      <c r="C22" t="n">
-        <v>-0.330263079262695</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="s">
-        <v>15</v>
-      </c>
-      <c r="B23" t="s">
-        <v>16</v>
-      </c>
-      <c r="C23" t="n">
-        <v>-1.75913045163046</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="s">
-        <v>15</v>
-      </c>
-      <c r="B24" t="s">
-        <v>16</v>
-      </c>
-      <c r="C24" t="n">
-        <v>-0.292749282980429</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="s">
-        <v>15</v>
-      </c>
-      <c r="B25" t="s">
-        <v>16</v>
-      </c>
-      <c r="C25" t="n">
-        <v>-0.479371952652629</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="s">
-        <v>15</v>
-      </c>
-      <c r="B26" t="s">
-        <v>16</v>
-      </c>
-      <c r="C26" t="n">
-        <v>-0.550612772039464</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="s">
-        <v>15</v>
-      </c>
-      <c r="B27" t="s">
-        <v>16</v>
-      </c>
-      <c r="C27" t="n">
-        <v>-0.293288295459016</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="s">
-        <v>15</v>
-      </c>
-      <c r="B28" t="s">
-        <v>16</v>
-      </c>
-      <c r="C28" t="n">
-        <v>-2.4238739196974</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="s">
-        <v>15</v>
-      </c>
-      <c r="B29" t="s">
-        <v>16</v>
-      </c>
-      <c r="C29" t="n">
-        <v>-0.658673349900634</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="s">
-        <v>15</v>
-      </c>
-      <c r="B30" t="s">
-        <v>16</v>
-      </c>
-      <c r="C30" t="n">
-        <v>-0.703699591505636</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="s">
-        <v>15</v>
-      </c>
-      <c r="B31" t="s">
-        <v>16</v>
-      </c>
-      <c r="C31" t="n">
-        <v>-0.918410309517611</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="s">
-        <v>15</v>
-      </c>
-      <c r="B32" t="s">
-        <v>16</v>
-      </c>
-      <c r="C32" t="n">
-        <v>-1.2573981293541</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="s">
-        <v>15</v>
-      </c>
-      <c r="B33" t="s">
-        <v>16</v>
-      </c>
-      <c r="C33" t="n">
-        <v>-1.51327928991041</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="s">
-        <v>15</v>
-      </c>
-      <c r="B34" t="s">
-        <v>16</v>
-      </c>
-      <c r="C34" t="n">
-        <v>-1.55068741521324</v>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="s">
-        <v>15</v>
-      </c>
-      <c r="B35" t="s">
-        <v>16</v>
-      </c>
-      <c r="C35" t="n">
-        <v>0.0396734055516748</v>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="s">
-        <v>15</v>
-      </c>
-      <c r="B36" t="s">
-        <v>16</v>
-      </c>
-      <c r="C36" t="n">
-        <v>-0.648444769327678</v>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="s">
-        <v>15</v>
-      </c>
-      <c r="B37" t="s">
-        <v>16</v>
-      </c>
-      <c r="C37" t="n">
-        <v>-0.0345027205631399</v>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="s">
-        <v>15</v>
-      </c>
-      <c r="B38" t="s">
-        <v>16</v>
-      </c>
-      <c r="C38" t="n">
-        <v>0.158658218944798</v>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="s">
-        <v>15</v>
-      </c>
-      <c r="B39" t="s">
-        <v>16</v>
-      </c>
-      <c r="C39" t="n">
-        <v>-0.388883784455958</v>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="s">
-        <v>15</v>
-      </c>
-      <c r="B40" t="s">
-        <v>16</v>
-      </c>
-      <c r="C40" t="n">
-        <v>-0.965840899386547</v>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="s">
-        <v>15</v>
-      </c>
-      <c r="B41" t="s">
-        <v>16</v>
-      </c>
-      <c r="C41" t="n">
-        <v>-1.0320766504746</v>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="s">
-        <v>15</v>
-      </c>
-      <c r="B42" t="s">
-        <v>16</v>
-      </c>
-      <c r="C42" t="n">
-        <v>-1.39768503539004</v>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="s">
-        <v>15</v>
-      </c>
-      <c r="B43" t="s">
-        <v>16</v>
-      </c>
-      <c r="C43" t="n">
-        <v>-0.824958546624859</v>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="s">
-        <v>15</v>
-      </c>
-      <c r="B44" t="s">
-        <v>16</v>
-      </c>
-      <c r="C44" t="n">
-        <v>-0.782067885394888</v>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="s">
-        <v>15</v>
-      </c>
-      <c r="B45" t="s">
-        <v>16</v>
-      </c>
-      <c r="C45" t="n">
-        <v>-0.198195689393404</v>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="s">
-        <v>15</v>
-      </c>
-      <c r="B46" t="s">
-        <v>16</v>
-      </c>
-      <c r="C46" t="n">
-        <v>-0.378647258537325</v>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="s">
-        <v>15</v>
-      </c>
-      <c r="B47" t="s">
-        <v>16</v>
-      </c>
-      <c r="C47" t="n">
-        <v>-1.8716635292068</v>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="s">
-        <v>15</v>
-      </c>
-      <c r="B48" t="s">
-        <v>16</v>
-      </c>
-      <c r="C48" t="n">
-        <v>-0.270333295984725</v>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="s">
-        <v>15</v>
-      </c>
-      <c r="B49" t="s">
-        <v>16</v>
-      </c>
-      <c r="C49" t="n">
-        <v>-0.446800300960166</v>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="s">
-        <v>15</v>
-      </c>
-      <c r="B50" t="s">
-        <v>16</v>
-      </c>
-      <c r="C50" t="n">
-        <v>0.0206431267823584</v>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="s">
-        <v>15</v>
-      </c>
-      <c r="B51" t="s">
-        <v>16</v>
-      </c>
-      <c r="C51" t="n">
-        <v>-0.031914488208344</v>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="s">
-        <v>15</v>
-      </c>
-      <c r="B52" t="s">
-        <v>16</v>
-      </c>
-      <c r="C52" t="n">
-        <v>-0.111517141284373</v>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="s">
-        <v>15</v>
-      </c>
-      <c r="B53" t="s">
-        <v>16</v>
-      </c>
-      <c r="C53" t="n">
-        <v>0.0317620159155274</v>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="s">
-        <v>15</v>
-      </c>
-      <c r="B54" t="s">
-        <v>16</v>
-      </c>
-      <c r="C54" t="n">
-        <v>-1.04740792465031</v>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" t="s">
-        <v>15</v>
-      </c>
-      <c r="B55" t="s">
-        <v>16</v>
-      </c>
-      <c r="C55" t="n">
-        <v>-1.4100203499374</v>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" t="s">
-        <v>15</v>
-      </c>
-      <c r="B56" t="s">
-        <v>16</v>
-      </c>
-      <c r="C56" t="n">
-        <v>-0.362697996929458</v>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" t="s">
-        <v>15</v>
-      </c>
-      <c r="B57" t="s">
-        <v>16</v>
-      </c>
-      <c r="C57" t="n">
-        <v>-0.070550106355934</v>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" t="s">
-        <v>15</v>
-      </c>
-      <c r="B58" t="s">
-        <v>16</v>
-      </c>
-      <c r="C58" t="n">
-        <v>-0.341199255656111</v>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" t="s">
-        <v>15</v>
-      </c>
-      <c r="B59" t="s">
-        <v>16</v>
-      </c>
-      <c r="C59" t="n">
-        <v>-0.433506067229178</v>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" t="s">
-        <v>15</v>
-      </c>
-      <c r="B60" t="s">
-        <v>16</v>
-      </c>
-      <c r="C60" t="n">
-        <v>-1.21153513654597</v>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" t="s">
-        <v>15</v>
-      </c>
-      <c r="B61" t="s">
-        <v>16</v>
-      </c>
-      <c r="C61" t="n">
-        <v>0.0774258415040324</v>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" t="s">
-        <v>15</v>
-      </c>
-      <c r="B62" t="s">
-        <v>16</v>
-      </c>
-      <c r="C62" t="n">
-        <v>-0.704259493897196</v>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" t="s">
-        <v>15</v>
-      </c>
-      <c r="B63" t="s">
-        <v>16</v>
-      </c>
-      <c r="C63" t="n">
-        <v>-0.757950071714979</v>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" t="s">
-        <v>15</v>
-      </c>
-      <c r="B64" t="s">
-        <v>16</v>
-      </c>
-      <c r="C64" t="n">
-        <v>-0.219890422018837</v>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" t="s">
-        <v>15</v>
-      </c>
-      <c r="B65" t="s">
-        <v>16</v>
-      </c>
-      <c r="C65" t="n">
-        <v>0.298613952559014</v>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" t="s">
-        <v>15</v>
-      </c>
-      <c r="B66" t="s">
-        <v>16</v>
-      </c>
-      <c r="C66" t="n">
-        <v>-0.832242264180278</v>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" t="s">
-        <v>15</v>
-      </c>
-      <c r="B67" t="s">
-        <v>16</v>
-      </c>
-      <c r="C67" t="n">
-        <v>-0.116781526942261</v>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" t="s">
-        <v>15</v>
-      </c>
-      <c r="B68" t="s">
-        <v>16</v>
-      </c>
-      <c r="C68" t="n">
-        <v>-0.558494740617521</v>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" t="s">
-        <v>15</v>
-      </c>
-      <c r="B69" t="s">
-        <v>16</v>
-      </c>
-      <c r="C69" t="n">
-        <v>-0.730194208918642</v>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" t="s">
-        <v>15</v>
-      </c>
-      <c r="B70" t="s">
-        <v>16</v>
-      </c>
-      <c r="C70" t="n">
-        <v>-1.09951602309663</v>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" t="s">
-        <v>15</v>
-      </c>
-      <c r="B71" t="s">
-        <v>16</v>
-      </c>
-      <c r="C71" t="n">
-        <v>-0.321838379451316</v>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" t="s">
-        <v>15</v>
-      </c>
-      <c r="B72" t="s">
-        <v>16</v>
-      </c>
-      <c r="C72" t="n">
-        <v>-1.47929469774811</v>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" t="s">
-        <v>15</v>
-      </c>
-      <c r="B73" t="s">
-        <v>16</v>
-      </c>
-      <c r="C73" t="n">
-        <v>-1.10123358299737</v>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" t="s">
-        <v>15</v>
-      </c>
-      <c r="B74" t="s">
-        <v>16</v>
-      </c>
-      <c r="C74" t="n">
-        <v>-0.198112461015282</v>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" t="s">
-        <v>15</v>
-      </c>
-      <c r="B75" t="s">
-        <v>16</v>
-      </c>
-      <c r="C75" t="n">
-        <v>-1.17342544487387</v>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" t="s">
-        <v>15</v>
-      </c>
-      <c r="B76" t="s">
-        <v>16</v>
-      </c>
-      <c r="C76" t="n">
-        <v>0.8915892241087</v>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" t="s">
-        <v>15</v>
-      </c>
-      <c r="B77" t="s">
-        <v>16</v>
-      </c>
-      <c r="C77" t="n">
-        <v>-2.0128869012536</v>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" t="s">
-        <v>15</v>
-      </c>
-      <c r="B78" t="s">
-        <v>16</v>
-      </c>
-      <c r="C78" t="n">
-        <v>-0.381702141392528</v>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" t="s">
-        <v>15</v>
-      </c>
-      <c r="B79" t="s">
-        <v>16</v>
-      </c>
-      <c r="C79" t="n">
-        <v>-2.23744277569863</v>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" t="s">
-        <v>15</v>
-      </c>
-      <c r="B80" t="s">
-        <v>16</v>
-      </c>
-      <c r="C80" t="n">
-        <v>-0.299040085261019</v>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" t="s">
-        <v>15</v>
-      </c>
-      <c r="B81" t="s">
-        <v>16</v>
-      </c>
-      <c r="C81" t="n">
-        <v>-1.22498526611613</v>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" t="s">
-        <v>15</v>
-      </c>
-      <c r="B82" t="s">
-        <v>16</v>
-      </c>
-      <c r="C82" t="n">
-        <v>-1.61674324840338</v>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" t="s">
-        <v>15</v>
-      </c>
-      <c r="B83" t="s">
-        <v>16</v>
-      </c>
-      <c r="C83" t="n">
-        <v>-0.230575453701432</v>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" t="s">
-        <v>15</v>
-      </c>
-      <c r="B84" t="s">
-        <v>16</v>
-      </c>
-      <c r="C84" t="n">
-        <v>-0.140235011649038</v>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" t="s">
-        <v>15</v>
-      </c>
-      <c r="B85" t="s">
-        <v>16</v>
-      </c>
-      <c r="C85" t="n">
-        <v>-0.704908030472586</v>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" t="s">
-        <v>15</v>
-      </c>
-      <c r="B86" t="s">
-        <v>16</v>
-      </c>
-      <c r="C86" t="n">
-        <v>-0.817326767040548</v>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" t="s">
-        <v>15</v>
-      </c>
-      <c r="B87" t="s">
-        <v>16</v>
-      </c>
-      <c r="C87" t="n">
-        <v>-0.50120019573813</v>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" t="s">
-        <v>15</v>
-      </c>
-      <c r="B88" t="s">
-        <v>16</v>
-      </c>
-      <c r="C88" t="n">
-        <v>-0.433493533556025</v>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" t="s">
-        <v>15</v>
-      </c>
-      <c r="B89" t="s">
-        <v>16</v>
-      </c>
-      <c r="C89" t="n">
-        <v>0.0906304498574328</v>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" t="s">
-        <v>15</v>
-      </c>
-      <c r="B90" t="s">
-        <v>16</v>
-      </c>
-      <c r="C90" t="n">
-        <v>-0.538265613176993</v>
-      </c>
-    </row>
-    <row r="91">
-      <c r="A91" t="s">
-        <v>15</v>
-      </c>
-      <c r="B91" t="s">
-        <v>16</v>
-      </c>
-      <c r="C91" t="n">
-        <v>-1.59327862552746</v>
-      </c>
-    </row>
-    <row r="92">
-      <c r="A92" t="s">
-        <v>15</v>
-      </c>
-      <c r="B92" t="s">
-        <v>16</v>
-      </c>
-      <c r="C92" t="n">
-        <v>-0.65292328047718</v>
-      </c>
-    </row>
-    <row r="93">
-      <c r="A93" t="s">
-        <v>15</v>
-      </c>
-      <c r="B93" t="s">
-        <v>16</v>
-      </c>
-      <c r="C93" t="n">
-        <v>-0.184965372267932</v>
-      </c>
-    </row>
-    <row r="94">
-      <c r="A94" t="s">
-        <v>15</v>
-      </c>
-      <c r="B94" t="s">
-        <v>16</v>
-      </c>
-      <c r="C94" t="n">
-        <v>-1.45910403812808</v>
-      </c>
-    </row>
-    <row r="95">
-      <c r="A95" t="s">
-        <v>15</v>
-      </c>
-      <c r="B95" t="s">
-        <v>16</v>
-      </c>
-      <c r="C95" t="n">
-        <v>-0.445657078687062</v>
-      </c>
-    </row>
-    <row r="96">
-      <c r="A96" t="s">
-        <v>15</v>
-      </c>
-      <c r="B96" t="s">
-        <v>16</v>
-      </c>
-      <c r="C96" t="n">
-        <v>-0.880971187923418</v>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97" t="s">
-        <v>15</v>
-      </c>
-      <c r="B97" t="s">
-        <v>16</v>
-      </c>
-      <c r="C97" t="n">
-        <v>0.228327626344892</v>
-      </c>
-    </row>
-    <row r="98">
-      <c r="A98" t="s">
-        <v>15</v>
-      </c>
-      <c r="B98" t="s">
-        <v>16</v>
-      </c>
-      <c r="C98" t="n">
-        <v>-1.14695704362054</v>
-      </c>
-    </row>
-    <row r="99">
-      <c r="A99" t="s">
-        <v>15</v>
-      </c>
-      <c r="B99" t="s">
-        <v>16</v>
-      </c>
-      <c r="C99" t="n">
-        <v>-1.42871415439955</v>
-      </c>
-    </row>
-    <row r="100">
-      <c r="A100" t="s">
-        <v>15</v>
-      </c>
-      <c r="B100" t="s">
-        <v>16</v>
-      </c>
-      <c r="C100" t="n">
-        <v>-0.52249348558055</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101" t="s">
-        <v>15</v>
-      </c>
-      <c r="B101" t="s">
-        <v>16</v>
-      </c>
-      <c r="C101" t="n">
-        <v>0.0115665554045393</v>
-      </c>
-    </row>
-    <row r="102">
-      <c r="A102" t="s">
-        <v>15</v>
-      </c>
-      <c r="B102" t="s">
-        <v>16</v>
-      </c>
-      <c r="C102" t="n">
-        <v>-1.19685952838085</v>
-      </c>
-    </row>
-    <row r="103">
-      <c r="A103" t="s">
-        <v>15</v>
-      </c>
-      <c r="B103" t="s">
-        <v>16</v>
-      </c>
-      <c r="C103" t="n">
-        <v>-0.613457448829368</v>
-      </c>
-    </row>
-    <row r="104">
-      <c r="A104" t="s">
-        <v>15</v>
-      </c>
-      <c r="B104" t="s">
-        <v>16</v>
-      </c>
-      <c r="C104" t="n">
-        <v>-0.288896712698689</v>
-      </c>
-    </row>
-    <row r="105">
-      <c r="A105" t="s">
-        <v>15</v>
-      </c>
-      <c r="B105" t="s">
-        <v>16</v>
-      </c>
-      <c r="C105" t="n">
-        <v>-0.99520558105436</v>
-      </c>
-    </row>
-    <row r="106">
-      <c r="A106" t="s">
-        <v>15</v>
-      </c>
-      <c r="B106" t="s">
-        <v>16</v>
-      </c>
-      <c r="C106" t="n">
-        <v>-1.31043546285532</v>
-      </c>
-    </row>
-    <row r="107">
-      <c r="A107" t="s">
-        <v>15</v>
-      </c>
-      <c r="B107" t="s">
-        <v>16</v>
-      </c>
-      <c r="C107" t="n">
-        <v>-1.0104060332074</v>
-      </c>
-    </row>
-    <row r="108">
-      <c r="A108" t="s">
-        <v>15</v>
-      </c>
-      <c r="B108" t="s">
-        <v>16</v>
-      </c>
-      <c r="C108" t="n">
-        <v>-0.0160133081461185</v>
-      </c>
-    </row>
-    <row r="109">
-      <c r="A109" t="s">
-        <v>15</v>
-      </c>
-      <c r="B109" t="s">
-        <v>16</v>
-      </c>
-      <c r="C109" t="n">
-        <v>0.00910990369887543</v>
-      </c>
-    </row>
-    <row r="110">
-      <c r="A110" t="s">
-        <v>15</v>
-      </c>
-      <c r="B110" t="s">
-        <v>16</v>
-      </c>
-      <c r="C110" t="n">
-        <v>-0.294830543139319</v>
-      </c>
-    </row>
-    <row r="111">
-      <c r="A111" t="s">
-        <v>15</v>
-      </c>
-      <c r="B111" t="s">
-        <v>16</v>
-      </c>
-      <c r="C111" t="n">
-        <v>-1.10602716927273</v>
-      </c>
-    </row>
-    <row r="112">
-      <c r="A112" t="s">
-        <v>15</v>
-      </c>
-      <c r="B112" t="s">
-        <v>16</v>
-      </c>
-      <c r="C112" t="n">
-        <v>-0.143742182516944</v>
-      </c>
-    </row>
-    <row r="113">
-      <c r="A113" t="s">
-        <v>15</v>
-      </c>
-      <c r="B113" t="s">
-        <v>16</v>
-      </c>
-      <c r="C113" t="n">
-        <v>-0.0416385436594562</v>
-      </c>
-    </row>
-    <row r="114">
-      <c r="A114" t="s">
-        <v>15</v>
-      </c>
-      <c r="B114" t="s">
-        <v>16</v>
-      </c>
-      <c r="C114" t="n">
-        <v>-0.349029863482234</v>
-      </c>
-    </row>
-    <row r="115">
-      <c r="A115" t="s">
-        <v>15</v>
-      </c>
-      <c r="B115" t="s">
-        <v>16</v>
-      </c>
-      <c r="C115" t="n">
-        <v>-0.0911159983046737</v>
-      </c>
-    </row>
-    <row r="116">
-      <c r="A116" t="s">
-        <v>15</v>
-      </c>
-      <c r="B116" t="s">
-        <v>16</v>
-      </c>
-      <c r="C116" t="n">
-        <v>-0.151728796649014</v>
-      </c>
-    </row>
-    <row r="117">
-      <c r="A117" t="s">
-        <v>15</v>
-      </c>
-      <c r="B117" t="s">
-        <v>16</v>
-      </c>
-      <c r="C117" t="n">
-        <v>-0.0323416524994173</v>
-      </c>
-    </row>
-    <row r="118">
-      <c r="A118" t="s">
-        <v>15</v>
-      </c>
-      <c r="B118" t="s">
-        <v>16</v>
-      </c>
-      <c r="C118" t="n">
-        <v>-0.874616166473846</v>
-      </c>
-    </row>
-    <row r="119">
-      <c r="A119" t="s">
-        <v>15</v>
-      </c>
-      <c r="B119" t="s">
-        <v>16</v>
-      </c>
-      <c r="C119" t="n">
-        <v>-0.0644654837820671</v>
-      </c>
-    </row>
-    <row r="120">
-      <c r="A120" t="s">
-        <v>15</v>
-      </c>
-      <c r="B120" t="s">
-        <v>16</v>
-      </c>
-      <c r="C120" t="n">
-        <v>-1.10944357343478</v>
-      </c>
-    </row>
-    <row r="121">
-      <c r="A121" t="s">
-        <v>15</v>
-      </c>
-      <c r="B121" t="s">
-        <v>16</v>
-      </c>
-      <c r="C121" t="n">
-        <v>-0.0179859422253963</v>
-      </c>
-    </row>
-    <row r="122">
-      <c r="A122" t="s">
-        <v>15</v>
-      </c>
-      <c r="B122" t="s">
-        <v>16</v>
-      </c>
-      <c r="C122" t="n">
-        <v>-0.847661681808276</v>
-      </c>
-    </row>
-    <row r="123">
-      <c r="A123" t="s">
-        <v>15</v>
-      </c>
-      <c r="B123" t="s">
-        <v>16</v>
-      </c>
-      <c r="C123" t="n">
-        <v>0.510687237452539</v>
-      </c>
-    </row>
-    <row r="124">
-      <c r="A124" t="s">
-        <v>15</v>
-      </c>
-      <c r="B124" t="s">
-        <v>16</v>
-      </c>
-      <c r="C124" t="n">
-        <v>0.539605712796246</v>
-      </c>
-    </row>
-    <row r="125">
-      <c r="A125" t="s">
-        <v>15</v>
-      </c>
-      <c r="B125" t="s">
-        <v>16</v>
-      </c>
-      <c r="C125" t="n">
-        <v>-0.597601204321732</v>
-      </c>
-    </row>
-    <row r="126">
-      <c r="A126" t="s">
-        <v>15</v>
-      </c>
-      <c r="B126" t="s">
-        <v>16</v>
-      </c>
-      <c r="C126" t="n">
-        <v>-1.26351303935537</v>
-      </c>
-    </row>
-    <row r="127">
-      <c r="A127" t="s">
-        <v>15</v>
-      </c>
-      <c r="B127" t="s">
-        <v>16</v>
-      </c>
-      <c r="C127" t="n">
-        <v>-2.13225624029738</v>
-      </c>
-    </row>
-    <row r="128">
-      <c r="A128" t="s">
-        <v>15</v>
-      </c>
-      <c r="B128" t="s">
-        <v>16</v>
-      </c>
-      <c r="C128" t="n">
-        <v>-0.804125956803401</v>
-      </c>
-    </row>
-    <row r="129">
-      <c r="A129" t="s">
-        <v>15</v>
-      </c>
-      <c r="B129" t="s">
-        <v>16</v>
-      </c>
-      <c r="C129" t="n">
-        <v>-0.736925929710294</v>
-      </c>
-    </row>
-    <row r="130">
-      <c r="A130" t="s">
-        <v>15</v>
-      </c>
-      <c r="B130" t="s">
-        <v>16</v>
-      </c>
-      <c r="C130" t="n">
-        <v>-0.386377101987293</v>
-      </c>
-    </row>
-    <row r="131">
-      <c r="A131" t="s">
-        <v>15</v>
-      </c>
-      <c r="B131" t="s">
-        <v>16</v>
-      </c>
-      <c r="C131" t="n">
-        <v>-1.58852591906496</v>
-      </c>
-    </row>
-    <row r="132">
-      <c r="A132" t="s">
-        <v>15</v>
-      </c>
-      <c r="B132" t="s">
-        <v>16</v>
-      </c>
-      <c r="C132" t="n">
-        <v>0.0469596249111347</v>
-      </c>
-    </row>
-    <row r="133">
-      <c r="A133" t="s">
-        <v>15</v>
-      </c>
-      <c r="B133" t="s">
-        <v>16</v>
-      </c>
-      <c r="C133" t="n">
-        <v>-1.2792937786375</v>
-      </c>
-    </row>
-    <row r="134">
-      <c r="A134" t="s">
-        <v>15</v>
-      </c>
-      <c r="B134" t="s">
-        <v>16</v>
-      </c>
-      <c r="C134" t="n">
-        <v>0.0574535481763129</v>
-      </c>
-    </row>
-    <row r="135">
-      <c r="A135" t="s">
-        <v>15</v>
-      </c>
-      <c r="B135" t="s">
-        <v>16</v>
-      </c>
-      <c r="C135" t="n">
-        <v>-0.114084324221058</v>
-      </c>
-    </row>
-    <row r="136">
-      <c r="A136" t="s">
-        <v>15</v>
-      </c>
-      <c r="B136" t="s">
-        <v>16</v>
-      </c>
-      <c r="C136" t="n">
-        <v>0.147210785787899</v>
-      </c>
-    </row>
-    <row r="137">
-      <c r="A137" t="s">
-        <v>15</v>
-      </c>
-      <c r="B137" t="s">
-        <v>16</v>
-      </c>
-      <c r="C137" t="n">
-        <v>-0.418214158580401</v>
-      </c>
-    </row>
-    <row r="138">
-      <c r="A138" t="s">
-        <v>15</v>
-      </c>
-      <c r="B138" t="s">
-        <v>16</v>
-      </c>
-      <c r="C138" t="n">
-        <v>-1.05829018456603</v>
-      </c>
-    </row>
-    <row r="139">
-      <c r="A139" t="s">
-        <v>15</v>
-      </c>
-      <c r="B139" t="s">
-        <v>16</v>
-      </c>
-      <c r="C139" t="n">
-        <v>0.181163237897837</v>
-      </c>
-    </row>
-    <row r="140">
-      <c r="A140" t="s">
-        <v>15</v>
-      </c>
-      <c r="B140" t="s">
-        <v>16</v>
-      </c>
-      <c r="C140" t="n">
-        <v>-1.09083627102378</v>
-      </c>
-    </row>
-    <row r="141">
-      <c r="A141" t="s">
-        <v>15</v>
-      </c>
-      <c r="B141" t="s">
-        <v>16</v>
-      </c>
-      <c r="C141" t="n">
-        <v>-0.562055318512082</v>
-      </c>
-    </row>
-    <row r="142">
-      <c r="A142" t="s">
-        <v>15</v>
-      </c>
-      <c r="B142" t="s">
-        <v>16</v>
-      </c>
-      <c r="C142" t="n">
-        <v>-0.623938425603641</v>
-      </c>
-    </row>
-    <row r="143">
-      <c r="A143" t="s">
-        <v>15</v>
-      </c>
-      <c r="B143" t="s">
-        <v>16</v>
-      </c>
-      <c r="C143" t="n">
-        <v>-0.339747149248755</v>
-      </c>
-    </row>
-    <row r="144">
-      <c r="A144" t="s">
-        <v>15</v>
-      </c>
-      <c r="B144" t="s">
-        <v>16</v>
-      </c>
-      <c r="C144" t="n">
-        <v>-1.21258750424799</v>
-      </c>
-    </row>
-    <row r="145">
-      <c r="A145" t="s">
-        <v>15</v>
-      </c>
-      <c r="B145" t="s">
-        <v>16</v>
-      </c>
-      <c r="C145" t="n">
-        <v>-0.285198779416414</v>
-      </c>
-    </row>
-    <row r="146">
-      <c r="A146" t="s">
-        <v>15</v>
-      </c>
-      <c r="B146" t="s">
-        <v>16</v>
-      </c>
-      <c r="C146" t="n">
-        <v>-1.53353006027658</v>
-      </c>
-    </row>
-    <row r="147">
-      <c r="A147" t="s">
-        <v>15</v>
-      </c>
-      <c r="B147" t="s">
-        <v>16</v>
-      </c>
-      <c r="C147" t="n">
-        <v>-0.955352554477703</v>
-      </c>
-    </row>
-    <row r="148">
-      <c r="A148" t="s">
-        <v>15</v>
-      </c>
-      <c r="B148" t="s">
-        <v>16</v>
-      </c>
-      <c r="C148" t="n">
-        <v>-1.03819477912299</v>
-      </c>
-    </row>
-    <row r="149">
-      <c r="A149" t="s">
-        <v>15</v>
-      </c>
-      <c r="B149" t="s">
-        <v>16</v>
-      </c>
-      <c r="C149" t="n">
-        <v>-0.46452536315598</v>
-      </c>
-    </row>
-    <row r="150">
-      <c r="A150" t="s">
-        <v>15</v>
-      </c>
-      <c r="B150" t="s">
-        <v>16</v>
-      </c>
-      <c r="C150" t="n">
-        <v>-0.802134492099662</v>
-      </c>
-    </row>
-    <row r="151">
-      <c r="A151" t="s">
-        <v>15</v>
-      </c>
-      <c r="B151" t="s">
-        <v>16</v>
-      </c>
-      <c r="C151" t="n">
-        <v>-0.536663287120794</v>
-      </c>
-    </row>
-    <row r="152">
-      <c r="A152" t="s">
-        <v>15</v>
-      </c>
-      <c r="B152" t="s">
-        <v>16</v>
-      </c>
-      <c r="C152" t="n">
-        <v>-0.00308795182675792</v>
-      </c>
-    </row>
-    <row r="153">
-      <c r="A153" t="s">
-        <v>15</v>
-      </c>
-      <c r="B153" t="s">
-        <v>16</v>
-      </c>
-      <c r="C153" t="n">
-        <v>-0.133538556588153</v>
-      </c>
-    </row>
-    <row r="154">
-      <c r="A154" t="s">
-        <v>15</v>
-      </c>
-      <c r="B154" t="s">
-        <v>16</v>
-      </c>
-      <c r="C154" t="n">
-        <v>-0.39696176666477</v>
-      </c>
-    </row>
-    <row r="155">
-      <c r="A155" t="s">
-        <v>15</v>
-      </c>
-      <c r="B155" t="s">
-        <v>16</v>
-      </c>
-      <c r="C155" t="n">
-        <v>0.290991487760081</v>
-      </c>
-    </row>
-    <row r="156">
-      <c r="A156" t="s">
-        <v>15</v>
-      </c>
-      <c r="B156" t="s">
-        <v>16</v>
-      </c>
-      <c r="C156" t="n">
-        <v>-1.08463790740202</v>
-      </c>
-    </row>
-    <row r="157">
-      <c r="A157" t="s">
-        <v>15</v>
-      </c>
-      <c r="B157" t="s">
-        <v>16</v>
-      </c>
-      <c r="C157" t="n">
-        <v>-0.606607131221151</v>
-      </c>
-    </row>
-    <row r="158">
-      <c r="A158" t="s">
-        <v>15</v>
-      </c>
-      <c r="B158" t="s">
-        <v>16</v>
-      </c>
-      <c r="C158" t="n">
-        <v>-1.08088055307038</v>
-      </c>
-    </row>
-    <row r="159">
-      <c r="A159" t="s">
-        <v>15</v>
-      </c>
-      <c r="B159" t="s">
-        <v>16</v>
-      </c>
-      <c r="C159" t="n">
-        <v>-0.295340822167245</v>
-      </c>
-    </row>
-    <row r="160">
-      <c r="A160" t="s">
-        <v>15</v>
-      </c>
-      <c r="B160" t="s">
-        <v>16</v>
-      </c>
-      <c r="C160" t="n">
-        <v>-0.509306011566451</v>
-      </c>
-    </row>
-    <row r="161">
-      <c r="A161" t="s">
-        <v>15</v>
-      </c>
-      <c r="B161" t="s">
-        <v>16</v>
-      </c>
-      <c r="C161" t="n">
-        <v>-0.311411677967745</v>
-      </c>
-    </row>
-    <row r="162">
-      <c r="A162" t="s">
-        <v>15</v>
-      </c>
-      <c r="B162" t="s">
-        <v>16</v>
-      </c>
-      <c r="C162" t="n">
-        <v>0.449663860251806</v>
-      </c>
-    </row>
-    <row r="163">
-      <c r="A163" t="s">
-        <v>15</v>
-      </c>
-      <c r="B163" t="s">
-        <v>16</v>
-      </c>
-      <c r="C163" t="n">
-        <v>-0.695842998623407</v>
-      </c>
-    </row>
-    <row r="164">
-      <c r="A164" t="s">
-        <v>15</v>
-      </c>
-      <c r="B164" t="s">
-        <v>16</v>
-      </c>
-      <c r="C164" t="n">
-        <v>-0.975034755160204</v>
-      </c>
-    </row>
-    <row r="165">
-      <c r="A165" t="s">
-        <v>15</v>
-      </c>
-      <c r="B165" t="s">
-        <v>16</v>
-      </c>
-      <c r="C165" t="n">
-        <v>0.251508400959435</v>
-      </c>
-    </row>
-    <row r="166">
-      <c r="A166" t="s">
-        <v>15</v>
-      </c>
-      <c r="B166" t="s">
-        <v>16</v>
-      </c>
-      <c r="C166" t="n">
-        <v>-0.391444574921028</v>
-      </c>
-    </row>
-    <row r="167">
-      <c r="A167" t="s">
-        <v>15</v>
-      </c>
-      <c r="B167" t="s">
-        <v>16</v>
-      </c>
-      <c r="C167" t="n">
-        <v>-0.527230650244975</v>
-      </c>
-    </row>
-    <row r="168">
-      <c r="A168" t="s">
-        <v>15</v>
-      </c>
-      <c r="B168" t="s">
-        <v>16</v>
-      </c>
-      <c r="C168" t="n">
-        <v>-0.405003740094082</v>
-      </c>
-    </row>
-    <row r="169">
-      <c r="A169" t="s">
-        <v>15</v>
-      </c>
-      <c r="B169" t="s">
-        <v>16</v>
-      </c>
-      <c r="C169" t="n">
-        <v>-0.450636434074088</v>
-      </c>
-    </row>
-    <row r="170">
-      <c r="A170" t="s">
-        <v>15</v>
-      </c>
-      <c r="B170" t="s">
-        <v>16</v>
-      </c>
-      <c r="C170" t="n">
-        <v>-1.80999935674838</v>
-      </c>
-    </row>
-    <row r="171">
-      <c r="A171" t="s">
-        <v>15</v>
-      </c>
-      <c r="B171" t="s">
-        <v>16</v>
-      </c>
-      <c r="C171" t="n">
-        <v>-0.109661115784863</v>
-      </c>
-    </row>
-    <row r="172">
-      <c r="A172" t="s">
-        <v>15</v>
-      </c>
-      <c r="B172" t="s">
-        <v>16</v>
-      </c>
-      <c r="C172" t="n">
-        <v>-1.76834654723752</v>
-      </c>
-    </row>
-    <row r="173">
-      <c r="A173" t="s">
-        <v>15</v>
-      </c>
-      <c r="B173" t="s">
-        <v>16</v>
-      </c>
-      <c r="C173" t="n">
-        <v>-0.843306434228236</v>
-      </c>
-    </row>
-    <row r="174">
-      <c r="A174" t="s">
-        <v>15</v>
-      </c>
-      <c r="B174" t="s">
-        <v>16</v>
-      </c>
-      <c r="C174" t="n">
-        <v>-1.27422123729237</v>
-      </c>
-    </row>
-    <row r="175">
-      <c r="A175" t="s">
-        <v>15</v>
-      </c>
-      <c r="B175" t="s">
-        <v>16</v>
-      </c>
-      <c r="C175" t="n">
-        <v>-0.690983547887255</v>
-      </c>
-    </row>
-    <row r="176">
-      <c r="A176" t="s">
-        <v>15</v>
-      </c>
-      <c r="B176" t="s">
-        <v>16</v>
-      </c>
-      <c r="C176" t="n">
-        <v>-0.356000432095889</v>
-      </c>
-    </row>
-    <row r="177">
-      <c r="A177" t="s">
-        <v>15</v>
-      </c>
-      <c r="B177" t="s">
-        <v>16</v>
-      </c>
-      <c r="C177" t="n">
-        <v>-0.489301851805832</v>
-      </c>
-    </row>
-    <row r="178">
-      <c r="A178" t="s">
-        <v>15</v>
-      </c>
-      <c r="B178" t="s">
-        <v>16</v>
-      </c>
-      <c r="C178" t="n">
-        <v>-0.237583573602721</v>
-      </c>
-    </row>
-    <row r="179">
-      <c r="A179" t="s">
-        <v>15</v>
-      </c>
-      <c r="B179" t="s">
-        <v>16</v>
-      </c>
-      <c r="C179" t="n">
-        <v>-0.816313780782745</v>
-      </c>
-    </row>
-    <row r="180">
-      <c r="A180" t="s">
-        <v>15</v>
-      </c>
-      <c r="B180" t="s">
-        <v>16</v>
-      </c>
-      <c r="C180" t="n">
-        <v>-0.22700373180258</v>
-      </c>
-    </row>
-    <row r="181">
-      <c r="A181" t="s">
-        <v>15</v>
-      </c>
-      <c r="B181" t="s">
-        <v>16</v>
-      </c>
-      <c r="C181" t="n">
-        <v>0.378376467503812</v>
-      </c>
-    </row>
-    <row r="182">
-      <c r="A182" t="s">
-        <v>15</v>
-      </c>
-      <c r="B182" t="s">
-        <v>16</v>
-      </c>
-      <c r="C182" t="n">
-        <v>-0.495037042624859</v>
-      </c>
-    </row>
-    <row r="183">
-      <c r="A183" t="s">
-        <v>15</v>
-      </c>
-      <c r="B183" t="s">
-        <v>16</v>
-      </c>
-      <c r="C183" t="n">
-        <v>-1.25366314436823</v>
-      </c>
-    </row>
-    <row r="184">
-      <c r="A184" t="s">
-        <v>15</v>
-      </c>
-      <c r="B184" t="s">
-        <v>16</v>
-      </c>
-      <c r="C184" t="n">
-        <v>-1.71431177588342</v>
-      </c>
-    </row>
-    <row r="185">
-      <c r="A185" t="s">
-        <v>15</v>
-      </c>
-      <c r="B185" t="s">
-        <v>16</v>
-      </c>
-      <c r="C185" t="n">
-        <v>-0.958653842384382</v>
-      </c>
-    </row>
-    <row r="186">
-      <c r="A186" t="s">
-        <v>15</v>
-      </c>
-      <c r="B186" t="s">
-        <v>16</v>
-      </c>
-      <c r="C186" t="n">
-        <v>-1.02372264594697</v>
-      </c>
-    </row>
-    <row r="187">
-      <c r="A187" t="s">
-        <v>15</v>
-      </c>
-      <c r="B187" t="s">
-        <v>16</v>
-      </c>
-      <c r="C187" t="n">
-        <v>-0.278922257082092</v>
-      </c>
-    </row>
-    <row r="188">
-      <c r="A188" t="s">
-        <v>15</v>
-      </c>
-      <c r="B188" t="s">
-        <v>16</v>
-      </c>
-      <c r="C188" t="n">
-        <v>-1.14764983929989</v>
-      </c>
-    </row>
-    <row r="189">
-      <c r="A189" t="s">
-        <v>15</v>
-      </c>
-      <c r="B189" t="s">
-        <v>16</v>
-      </c>
-      <c r="C189" t="n">
-        <v>-1.05073033089373</v>
-      </c>
-    </row>
-    <row r="190">
-      <c r="A190" t="s">
-        <v>15</v>
-      </c>
-      <c r="B190" t="s">
-        <v>16</v>
-      </c>
-      <c r="C190" t="n">
-        <v>0.326212187521919</v>
-      </c>
-    </row>
-    <row r="191">
-      <c r="A191" t="s">
-        <v>15</v>
-      </c>
-      <c r="B191" t="s">
-        <v>16</v>
-      </c>
-      <c r="C191" t="n">
-        <v>0.0959364188009504</v>
-      </c>
-    </row>
-    <row r="192">
-      <c r="A192" t="s">
-        <v>15</v>
-      </c>
-      <c r="B192" t="s">
-        <v>16</v>
-      </c>
-      <c r="C192" t="n">
-        <v>-0.00253540321448309</v>
-      </c>
-    </row>
-    <row r="193">
-      <c r="A193" t="s">
-        <v>15</v>
-      </c>
-      <c r="B193" t="s">
-        <v>16</v>
-      </c>
-      <c r="C193" t="n">
-        <v>-1.37535740912902</v>
-      </c>
-    </row>
-    <row r="194">
-      <c r="A194" t="s">
-        <v>15</v>
-      </c>
-      <c r="B194" t="s">
-        <v>16</v>
-      </c>
-      <c r="C194" t="n">
-        <v>0.315171746347784</v>
-      </c>
-    </row>
-    <row r="195">
-      <c r="A195" t="s">
-        <v>15</v>
-      </c>
-      <c r="B195" t="s">
-        <v>16</v>
-      </c>
-      <c r="C195" t="n">
-        <v>-0.734099009972823</v>
-      </c>
-    </row>
-    <row r="196">
-      <c r="A196" t="s">
-        <v>15</v>
-      </c>
-      <c r="B196" t="s">
-        <v>16</v>
-      </c>
-      <c r="C196" t="n">
-        <v>-0.932678213529006</v>
-      </c>
-    </row>
-    <row r="197">
-      <c r="A197" t="s">
-        <v>15</v>
-      </c>
-      <c r="B197" t="s">
-        <v>16</v>
-      </c>
-      <c r="C197" t="n">
-        <v>-1.38629213422071</v>
-      </c>
-    </row>
-    <row r="198">
-      <c r="A198" t="s">
-        <v>15</v>
-      </c>
-      <c r="B198" t="s">
-        <v>16</v>
-      </c>
-      <c r="C198" t="n">
-        <v>-0.298038392910699</v>
-      </c>
-    </row>
-    <row r="199">
-      <c r="A199" t="s">
-        <v>15</v>
-      </c>
-      <c r="B199" t="s">
-        <v>16</v>
-      </c>
-      <c r="C199" t="n">
-        <v>-0.86155978299096</v>
-      </c>
-    </row>
-    <row r="200">
-      <c r="A200" t="s">
-        <v>15</v>
-      </c>
-      <c r="B200" t="s">
-        <v>16</v>
-      </c>
-      <c r="C200" t="n">
-        <v>-0.121494900435445</v>
-      </c>
-    </row>
-    <row r="201">
-      <c r="A201" t="s">
-        <v>15</v>
-      </c>
-      <c r="B201" t="s">
-        <v>16</v>
-      </c>
-      <c r="C201" t="n">
-        <v>-0.603333607154608</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
@@ -3283,7 +1045,7 @@
         <v>517.34</v>
       </c>
       <c r="E2" t="n">
-        <v>354.220065129759</v>
+        <v>406.754496112247</v>
       </c>
     </row>
     <row r="3">
@@ -3300,7 +1062,7 @@
         <v>1517.85</v>
       </c>
       <c r="E3" t="n">
-        <v>266.906496319253</v>
+        <v>271.720207524288</v>
       </c>
     </row>
     <row r="4">
@@ -3317,7 +1079,7 @@
         <v>2790.83</v>
       </c>
       <c r="E4" t="n">
-        <v>122.657888252699</v>
+        <v>122.658099067329</v>
       </c>
     </row>
     <row r="5">
@@ -3334,7 +1096,7 @@
         <v>739.459999999999</v>
       </c>
       <c r="E5" t="n">
-        <v>-506.645932162956</v>
+        <v>-524.830354496172</v>
       </c>
     </row>
     <row r="6">
@@ -3351,7 +1113,7 @@
         <v>1179</v>
       </c>
       <c r="E6" t="n">
-        <v>-356.267485530213</v>
+        <v>-511.249887782177</v>
       </c>
     </row>
     <row r="7">
@@ -3368,7 +1130,7 @@
         <v>682.55</v>
       </c>
       <c r="E7" t="n">
-        <v>411.984553154748</v>
+        <v>211.660078631605</v>
       </c>
     </row>
     <row r="8">
@@ -3385,7 +1147,7 @@
         <v>-171.76</v>
       </c>
       <c r="E8" t="n">
-        <v>459.848495562085</v>
+        <v>452.681968958766</v>
       </c>
     </row>
     <row r="9">
@@ -3402,7 +1164,7 @@
         <v>854.04</v>
       </c>
       <c r="E9" t="n">
-        <v>287.517206527921</v>
+        <v>549.733439054115</v>
       </c>
     </row>
     <row r="10">
@@ -3419,7 +1181,7 @@
         <v>-1503.6</v>
       </c>
       <c r="E10" t="n">
-        <v>298.937619359286</v>
+        <v>226.69607776473</v>
       </c>
     </row>
     <row r="11">
@@ -3436,7 +1198,7 @@
         <v>-88.7199999999993</v>
       </c>
       <c r="E11" t="n">
-        <v>-1102.85808534649</v>
+        <v>-1058.6196028939</v>
       </c>
     </row>
     <row r="12">
@@ -3453,7 +1215,7 @@
         <v>-2305.05</v>
       </c>
       <c r="E12" t="n">
-        <v>-330.399182519383</v>
+        <v>-331.530553273686</v>
       </c>
     </row>
     <row r="13">
@@ -3470,7 +1232,7 @@
         <v>-1179.58</v>
       </c>
       <c r="E13" t="n">
-        <v>-997.430459160965</v>
+        <v>-984.948297408981</v>
       </c>
     </row>
     <row r="14">
@@ -3487,7 +1249,7 @@
         <v>-1491.94</v>
       </c>
       <c r="E14" t="n">
-        <v>513.461326809087</v>
+        <v>451.438297245348</v>
       </c>
     </row>
     <row r="15">
@@ -3504,7 +1266,7 @@
         <v>-1081</v>
       </c>
       <c r="E15" t="n">
-        <v>-3152.85112777756</v>
+        <v>-3025.51746873038</v>
       </c>
     </row>
   </sheetData>
@@ -3597,10 +1359,10 @@
         <v>40</v>
       </c>
       <c r="D5" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E5" t="n">
-        <v>0.928571428571429</v>
+        <v>0.857142857142857</v>
       </c>
     </row>
     <row r="6">
@@ -3665,10 +1427,10 @@
         <v>44</v>
       </c>
       <c r="D9" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E9" t="n">
-        <v>0.785714285714286</v>
+        <v>0.857142857142857</v>
       </c>
     </row>
     <row r="10">
@@ -3682,10 +1444,10 @@
         <v>45</v>
       </c>
       <c r="D10" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E10" t="n">
-        <v>0.785714285714286</v>
+        <v>0.857142857142857</v>
       </c>
     </row>
     <row r="11">
@@ -3699,10 +1461,10 @@
         <v>46</v>
       </c>
       <c r="D11" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E11" t="n">
-        <v>0.714285714285714</v>
+        <v>0.785714285714286</v>
       </c>
     </row>
     <row r="12">
@@ -3767,10 +1529,10 @@
         <v>50</v>
       </c>
       <c r="D15" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E15" t="n">
-        <v>0.642857142857143</v>
+        <v>0.714285714285714</v>
       </c>
     </row>
     <row r="16">
@@ -3784,10 +1546,10 @@
         <v>51</v>
       </c>
       <c r="D16" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E16" t="n">
-        <v>0.571428571428571</v>
+        <v>0.642857142857143</v>
       </c>
     </row>
     <row r="17">
@@ -3818,10 +1580,10 @@
         <v>53</v>
       </c>
       <c r="D18" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E18" t="n">
-        <v>0.571428571428571</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="19">
@@ -3835,10 +1597,10 @@
         <v>54</v>
       </c>
       <c r="D19" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E19" t="n">
-        <v>0.571428571428571</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="20">
@@ -3852,10 +1614,10 @@
         <v>55</v>
       </c>
       <c r="D20" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E20" t="n">
-        <v>0.571428571428571</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="21">
@@ -3869,10 +1631,10 @@
         <v>56</v>
       </c>
       <c r="D21" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E21" t="n">
-        <v>0.5</v>
+        <v>0.428571428571429</v>
       </c>
     </row>
     <row r="22">
@@ -3886,10 +1648,10 @@
         <v>57</v>
       </c>
       <c r="D22" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E22" t="n">
-        <v>0.5</v>
+        <v>0.428571428571429</v>
       </c>
     </row>
     <row r="23">
@@ -3903,10 +1665,10 @@
         <v>58</v>
       </c>
       <c r="D23" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E23" t="n">
-        <v>0.5</v>
+        <v>0.428571428571429</v>
       </c>
     </row>
     <row r="24">
@@ -3920,10 +1682,10 @@
         <v>59</v>
       </c>
       <c r="D24" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E24" t="n">
-        <v>0.5</v>
+        <v>0.428571428571429</v>
       </c>
     </row>
     <row r="25">
@@ -3937,10 +1699,10 @@
         <v>60</v>
       </c>
       <c r="D25" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E25" t="n">
-        <v>0.5</v>
+        <v>0.428571428571429</v>
       </c>
     </row>
     <row r="26">
@@ -3954,10 +1716,10 @@
         <v>61</v>
       </c>
       <c r="D26" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E26" t="n">
-        <v>0.5</v>
+        <v>0.357142857142857</v>
       </c>
     </row>
     <row r="27">
@@ -3971,10 +1733,10 @@
         <v>62</v>
       </c>
       <c r="D27" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E27" t="n">
-        <v>0.5</v>
+        <v>0.357142857142857</v>
       </c>
     </row>
     <row r="28">
@@ -3988,10 +1750,10 @@
         <v>63</v>
       </c>
       <c r="D28" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E28" t="n">
-        <v>0.428571428571429</v>
+        <v>0.357142857142857</v>
       </c>
     </row>
     <row r="29">
@@ -4005,10 +1767,10 @@
         <v>64</v>
       </c>
       <c r="D29" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E29" t="n">
-        <v>0.428571428571429</v>
+        <v>0.357142857142857</v>
       </c>
     </row>
     <row r="30">
@@ -4022,10 +1784,10 @@
         <v>65</v>
       </c>
       <c r="D30" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E30" t="n">
-        <v>0.428571428571429</v>
+        <v>0.357142857142857</v>
       </c>
     </row>
     <row r="31">
@@ -4039,10 +1801,10 @@
         <v>66</v>
       </c>
       <c r="D31" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E31" t="n">
-        <v>0.357142857142857</v>
+        <v>0.285714285714286</v>
       </c>
     </row>
     <row r="32">
@@ -4056,10 +1818,10 @@
         <v>67</v>
       </c>
       <c r="D32" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E32" t="n">
-        <v>0.357142857142857</v>
+        <v>0.285714285714286</v>
       </c>
     </row>
     <row r="33">
@@ -4073,10 +1835,10 @@
         <v>68</v>
       </c>
       <c r="D33" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E33" t="n">
-        <v>0.357142857142857</v>
+        <v>0.214285714285714</v>
       </c>
     </row>
     <row r="34">
@@ -4090,10 +1852,10 @@
         <v>69</v>
       </c>
       <c r="D34" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E34" t="n">
-        <v>0.285714285714286</v>
+        <v>0.214285714285714</v>
       </c>
     </row>
     <row r="35">
@@ -4107,10 +1869,10 @@
         <v>70</v>
       </c>
       <c r="D35" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E35" t="n">
-        <v>0.285714285714286</v>
+        <v>0.214285714285714</v>
       </c>
     </row>
     <row r="36">
@@ -4124,10 +1886,10 @@
         <v>71</v>
       </c>
       <c r="D36" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E36" t="n">
-        <v>0.285714285714286</v>
+        <v>0.214285714285714</v>
       </c>
     </row>
     <row r="37">
@@ -4141,10 +1903,10 @@
         <v>72</v>
       </c>
       <c r="D37" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E37" t="n">
-        <v>0.285714285714286</v>
+        <v>0.214285714285714</v>
       </c>
     </row>
     <row r="38">
@@ -4158,10 +1920,10 @@
         <v>73</v>
       </c>
       <c r="D38" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E38" t="n">
-        <v>0.285714285714286</v>
+        <v>0.214285714285714</v>
       </c>
     </row>
     <row r="39">
@@ -4175,10 +1937,10 @@
         <v>74</v>
       </c>
       <c r="D39" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E39" t="n">
-        <v>0.285714285714286</v>
+        <v>0.214285714285714</v>
       </c>
     </row>
     <row r="40">
@@ -4192,10 +1954,10 @@
         <v>75</v>
       </c>
       <c r="D40" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E40" t="n">
-        <v>0.285714285714286</v>
+        <v>0.214285714285714</v>
       </c>
     </row>
     <row r="41">
@@ -4209,10 +1971,10 @@
         <v>76</v>
       </c>
       <c r="D41" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E41" t="n">
-        <v>0.285714285714286</v>
+        <v>0.214285714285714</v>
       </c>
     </row>
     <row r="42">
@@ -4226,10 +1988,10 @@
         <v>77</v>
       </c>
       <c r="D42" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E42" t="n">
-        <v>0.285714285714286</v>
+        <v>0.214285714285714</v>
       </c>
     </row>
     <row r="43">
@@ -4243,10 +2005,10 @@
         <v>78</v>
       </c>
       <c r="D43" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E43" t="n">
-        <v>0.285714285714286</v>
+        <v>0.142857142857143</v>
       </c>
     </row>
     <row r="44">
@@ -4260,10 +2022,10 @@
         <v>79</v>
       </c>
       <c r="D44" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E44" t="n">
-        <v>0.214285714285714</v>
+        <v>0.142857142857143</v>
       </c>
     </row>
     <row r="45">
@@ -4277,10 +2039,10 @@
         <v>80</v>
       </c>
       <c r="D45" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E45" t="n">
-        <v>0.214285714285714</v>
+        <v>0.142857142857143</v>
       </c>
     </row>
     <row r="46">
@@ -4294,10 +2056,10 @@
         <v>81</v>
       </c>
       <c r="D46" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E46" t="n">
-        <v>0.214285714285714</v>
+        <v>0.142857142857143</v>
       </c>
     </row>
     <row r="47">
@@ -4311,10 +2073,10 @@
         <v>82</v>
       </c>
       <c r="D47" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E47" t="n">
-        <v>0.214285714285714</v>
+        <v>0.142857142857143</v>
       </c>
     </row>
     <row r="48">
@@ -4328,10 +2090,10 @@
         <v>83</v>
       </c>
       <c r="D48" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E48" t="n">
-        <v>0.214285714285714</v>
+        <v>0.142857142857143</v>
       </c>
     </row>
     <row r="49">
@@ -4345,10 +2107,10 @@
         <v>84</v>
       </c>
       <c r="D49" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E49" t="n">
-        <v>0.214285714285714</v>
+        <v>0.142857142857143</v>
       </c>
     </row>
     <row r="50">
@@ -4498,10 +2260,10 @@
         <v>93</v>
       </c>
       <c r="D58" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E58" t="n">
-        <v>0.142857142857143</v>
+        <v>0.0714285714285714</v>
       </c>
     </row>
     <row r="59">
@@ -4515,10 +2277,10 @@
         <v>94</v>
       </c>
       <c r="D59" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E59" t="n">
-        <v>0.142857142857143</v>
+        <v>0.0714285714285714</v>
       </c>
     </row>
     <row r="60">
@@ -4532,10 +2294,10 @@
         <v>95</v>
       </c>
       <c r="D60" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E60" t="n">
-        <v>0.142857142857143</v>
+        <v>0.0714285714285714</v>
       </c>
     </row>
     <row r="61">
@@ -4549,10 +2311,10 @@
         <v>96</v>
       </c>
       <c r="D61" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E61" t="n">
-        <v>0.142857142857143</v>
+        <v>0.0714285714285714</v>
       </c>
     </row>
     <row r="62">
@@ -4566,10 +2328,10 @@
         <v>97</v>
       </c>
       <c r="D62" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E62" t="n">
-        <v>0.142857142857143</v>
+        <v>0.0714285714285714</v>
       </c>
     </row>
     <row r="63">
@@ -4583,10 +2345,10 @@
         <v>98</v>
       </c>
       <c r="D63" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E63" t="n">
-        <v>0.142857142857143</v>
+        <v>0.0714285714285714</v>
       </c>
     </row>
     <row r="64">
@@ -4600,10 +2362,10 @@
         <v>99</v>
       </c>
       <c r="D64" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E64" t="n">
-        <v>0.142857142857143</v>
+        <v>0.0714285714285714</v>
       </c>
     </row>
     <row r="65">
@@ -4617,10 +2379,10 @@
         <v>100</v>
       </c>
       <c r="D65" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E65" t="n">
-        <v>0.142857142857143</v>
+        <v>0.0714285714285714</v>
       </c>
     </row>
     <row r="66">
@@ -5912,176 +3674,6 @@
         <v>1</v>
       </c>
       <c r="E141" t="n">
-        <v>0.0714285714285714</v>
-      </c>
-    </row>
-    <row r="142">
-      <c r="A142" t="s">
-        <v>15</v>
-      </c>
-      <c r="B142" t="s">
-        <v>16</v>
-      </c>
-      <c r="C142" t="s">
-        <v>177</v>
-      </c>
-      <c r="D142" t="n">
-        <v>1</v>
-      </c>
-      <c r="E142" t="n">
-        <v>0.0714285714285714</v>
-      </c>
-    </row>
-    <row r="143">
-      <c r="A143" t="s">
-        <v>15</v>
-      </c>
-      <c r="B143" t="s">
-        <v>16</v>
-      </c>
-      <c r="C143" t="s">
-        <v>178</v>
-      </c>
-      <c r="D143" t="n">
-        <v>1</v>
-      </c>
-      <c r="E143" t="n">
-        <v>0.0714285714285714</v>
-      </c>
-    </row>
-    <row r="144">
-      <c r="A144" t="s">
-        <v>15</v>
-      </c>
-      <c r="B144" t="s">
-        <v>16</v>
-      </c>
-      <c r="C144" t="s">
-        <v>179</v>
-      </c>
-      <c r="D144" t="n">
-        <v>1</v>
-      </c>
-      <c r="E144" t="n">
-        <v>0.0714285714285714</v>
-      </c>
-    </row>
-    <row r="145">
-      <c r="A145" t="s">
-        <v>15</v>
-      </c>
-      <c r="B145" t="s">
-        <v>16</v>
-      </c>
-      <c r="C145" t="s">
-        <v>180</v>
-      </c>
-      <c r="D145" t="n">
-        <v>1</v>
-      </c>
-      <c r="E145" t="n">
-        <v>0.0714285714285714</v>
-      </c>
-    </row>
-    <row r="146">
-      <c r="A146" t="s">
-        <v>15</v>
-      </c>
-      <c r="B146" t="s">
-        <v>16</v>
-      </c>
-      <c r="C146" t="s">
-        <v>181</v>
-      </c>
-      <c r="D146" t="n">
-        <v>1</v>
-      </c>
-      <c r="E146" t="n">
-        <v>0.0714285714285714</v>
-      </c>
-    </row>
-    <row r="147">
-      <c r="A147" t="s">
-        <v>15</v>
-      </c>
-      <c r="B147" t="s">
-        <v>16</v>
-      </c>
-      <c r="C147" t="s">
-        <v>182</v>
-      </c>
-      <c r="D147" t="n">
-        <v>1</v>
-      </c>
-      <c r="E147" t="n">
-        <v>0.0714285714285714</v>
-      </c>
-    </row>
-    <row r="148">
-      <c r="A148" t="s">
-        <v>15</v>
-      </c>
-      <c r="B148" t="s">
-        <v>16</v>
-      </c>
-      <c r="C148" t="s">
-        <v>183</v>
-      </c>
-      <c r="D148" t="n">
-        <v>1</v>
-      </c>
-      <c r="E148" t="n">
-        <v>0.0714285714285714</v>
-      </c>
-    </row>
-    <row r="149">
-      <c r="A149" t="s">
-        <v>15</v>
-      </c>
-      <c r="B149" t="s">
-        <v>16</v>
-      </c>
-      <c r="C149" t="s">
-        <v>184</v>
-      </c>
-      <c r="D149" t="n">
-        <v>1</v>
-      </c>
-      <c r="E149" t="n">
-        <v>0.0714285714285714</v>
-      </c>
-    </row>
-    <row r="150">
-      <c r="A150" t="s">
-        <v>15</v>
-      </c>
-      <c r="B150" t="s">
-        <v>16</v>
-      </c>
-      <c r="C150" t="s">
-        <v>185</v>
-      </c>
-      <c r="D150" t="n">
-        <v>1</v>
-      </c>
-      <c r="E150" t="n">
-        <v>0.0714285714285714</v>
-      </c>
-    </row>
-    <row r="151">
-      <c r="A151" t="s">
-        <v>15</v>
-      </c>
-      <c r="B151" t="s">
-        <v>16</v>
-      </c>
-      <c r="C151" t="s">
-        <v>186</v>
-      </c>
-      <c r="D151" t="n">
-        <v>1</v>
-      </c>
-      <c r="E151" t="n">
         <v>0.0714285714285714</v>
       </c>
     </row>

--- a/05_Figures/F06_prediction/proteins/trajectory/d_fcsa_II/spls/c_data/results.xlsx
+++ b/05_Figures/F06_prediction/proteins/trajectory/d_fcsa_II/spls/c_data/results.xlsx
@@ -968,7 +968,7 @@
         <v>5696</v>
       </c>
       <c r="G3" t="n">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="H3" t="n">
         <v>-0.131188602948822</v>
@@ -976,10 +976,18 @@
       <c r="I3" t="n">
         <v>0.103296703296703</v>
       </c>
-      <c r="J3"/>
-      <c r="K3"/>
-      <c r="L3"/>
-      <c r="M3"/>
+      <c r="J3" t="n">
+        <v>0.203980099502488</v>
+      </c>
+      <c r="K3" t="n">
+        <v>0.278606965174129</v>
+      </c>
+      <c r="L3" t="n">
+        <v>-0.634561754642713</v>
+      </c>
+      <c r="M3" t="n">
+        <v>0.633388489296064</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1003,6 +1011,2206 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2">
+      <c r="A2" t="s">
+        <v>15</v>
+      </c>
+      <c r="B2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C2" t="n">
+        <v>-0.81110606722582</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s">
+        <v>15</v>
+      </c>
+      <c r="B3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C3" t="n">
+        <v>-0.799270049228189</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s">
+        <v>15</v>
+      </c>
+      <c r="B4" t="s">
+        <v>16</v>
+      </c>
+      <c r="C4" t="n">
+        <v>-1.20298841694542</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="s">
+        <v>15</v>
+      </c>
+      <c r="B5" t="s">
+        <v>16</v>
+      </c>
+      <c r="C5" t="n">
+        <v>-1.01787061617362</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="s">
+        <v>15</v>
+      </c>
+      <c r="B6" t="s">
+        <v>16</v>
+      </c>
+      <c r="C6" t="n">
+        <v>-0.547953866424526</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="s">
+        <v>15</v>
+      </c>
+      <c r="B7" t="s">
+        <v>16</v>
+      </c>
+      <c r="C7" t="n">
+        <v>-0.55317563521634</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="s">
+        <v>15</v>
+      </c>
+      <c r="B8" t="s">
+        <v>16</v>
+      </c>
+      <c r="C8" t="n">
+        <v>-0.306571132299133</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="s">
+        <v>15</v>
+      </c>
+      <c r="B9" t="s">
+        <v>16</v>
+      </c>
+      <c r="C9" t="n">
+        <v>0.543500706435345</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="s">
+        <v>15</v>
+      </c>
+      <c r="B10" t="s">
+        <v>16</v>
+      </c>
+      <c r="C10" t="n">
+        <v>-0.685999703174605</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="s">
+        <v>15</v>
+      </c>
+      <c r="B11" t="s">
+        <v>16</v>
+      </c>
+      <c r="C11" t="n">
+        <v>-1.10770488266343</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="s">
+        <v>15</v>
+      </c>
+      <c r="B12" t="s">
+        <v>16</v>
+      </c>
+      <c r="C12" t="n">
+        <v>-0.196591975075371</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="s">
+        <v>15</v>
+      </c>
+      <c r="B13" t="s">
+        <v>16</v>
+      </c>
+      <c r="C13" t="n">
+        <v>-0.697853292083839</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="s">
+        <v>15</v>
+      </c>
+      <c r="B14" t="s">
+        <v>16</v>
+      </c>
+      <c r="C14" t="n">
+        <v>-0.955154242725512</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="s">
+        <v>15</v>
+      </c>
+      <c r="B15" t="s">
+        <v>16</v>
+      </c>
+      <c r="C15" t="n">
+        <v>0.105949547888923</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="s">
+        <v>15</v>
+      </c>
+      <c r="B16" t="s">
+        <v>16</v>
+      </c>
+      <c r="C16" t="n">
+        <v>0.165993233302617</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="s">
+        <v>15</v>
+      </c>
+      <c r="B17" t="s">
+        <v>16</v>
+      </c>
+      <c r="C17" t="n">
+        <v>0.194642644842011</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="s">
+        <v>15</v>
+      </c>
+      <c r="B18" t="s">
+        <v>16</v>
+      </c>
+      <c r="C18" t="n">
+        <v>-0.0828652581986544</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="s">
+        <v>15</v>
+      </c>
+      <c r="B19" t="s">
+        <v>16</v>
+      </c>
+      <c r="C19" t="n">
+        <v>-0.513895660717743</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="s">
+        <v>15</v>
+      </c>
+      <c r="B20" t="s">
+        <v>16</v>
+      </c>
+      <c r="C20" t="n">
+        <v>-0.46098783848474</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="s">
+        <v>15</v>
+      </c>
+      <c r="B21" t="s">
+        <v>16</v>
+      </c>
+      <c r="C21" t="n">
+        <v>-0.542444065377026</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="s">
+        <v>15</v>
+      </c>
+      <c r="B22" t="s">
+        <v>16</v>
+      </c>
+      <c r="C22" t="n">
+        <v>-0.181442304461106</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="s">
+        <v>15</v>
+      </c>
+      <c r="B23" t="s">
+        <v>16</v>
+      </c>
+      <c r="C23" t="n">
+        <v>-2.0763920273716</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="s">
+        <v>15</v>
+      </c>
+      <c r="B24" t="s">
+        <v>16</v>
+      </c>
+      <c r="C24" t="n">
+        <v>-0.340114963417162</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="s">
+        <v>15</v>
+      </c>
+      <c r="B25" t="s">
+        <v>16</v>
+      </c>
+      <c r="C25" t="n">
+        <v>-0.52602430677603</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="s">
+        <v>15</v>
+      </c>
+      <c r="B26" t="s">
+        <v>16</v>
+      </c>
+      <c r="C26" t="n">
+        <v>-0.598022624948925</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="s">
+        <v>15</v>
+      </c>
+      <c r="B27" t="s">
+        <v>16</v>
+      </c>
+      <c r="C27" t="n">
+        <v>-0.311502504251303</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="s">
+        <v>15</v>
+      </c>
+      <c r="B28" t="s">
+        <v>16</v>
+      </c>
+      <c r="C28" t="n">
+        <v>-1.79731372140788</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="s">
+        <v>15</v>
+      </c>
+      <c r="B29" t="s">
+        <v>16</v>
+      </c>
+      <c r="C29" t="n">
+        <v>-0.633850348532039</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="s">
+        <v>15</v>
+      </c>
+      <c r="B30" t="s">
+        <v>16</v>
+      </c>
+      <c r="C30" t="n">
+        <v>-0.495658228563922</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="s">
+        <v>15</v>
+      </c>
+      <c r="B31" t="s">
+        <v>16</v>
+      </c>
+      <c r="C31" t="n">
+        <v>-0.906505240944399</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="s">
+        <v>15</v>
+      </c>
+      <c r="B32" t="s">
+        <v>16</v>
+      </c>
+      <c r="C32" t="n">
+        <v>-1.27492527041741</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="s">
+        <v>15</v>
+      </c>
+      <c r="B33" t="s">
+        <v>16</v>
+      </c>
+      <c r="C33" t="n">
+        <v>-2.56612006242058</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="s">
+        <v>15</v>
+      </c>
+      <c r="B34" t="s">
+        <v>16</v>
+      </c>
+      <c r="C34" t="n">
+        <v>-1.68568661198642</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="s">
+        <v>15</v>
+      </c>
+      <c r="B35" t="s">
+        <v>16</v>
+      </c>
+      <c r="C35" t="n">
+        <v>-0.0661932030387575</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="s">
+        <v>15</v>
+      </c>
+      <c r="B36" t="s">
+        <v>16</v>
+      </c>
+      <c r="C36" t="n">
+        <v>-0.745888385847166</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="s">
+        <v>15</v>
+      </c>
+      <c r="B37" t="s">
+        <v>16</v>
+      </c>
+      <c r="C37" t="n">
+        <v>-0.142799329854996</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="s">
+        <v>15</v>
+      </c>
+      <c r="B38" t="s">
+        <v>16</v>
+      </c>
+      <c r="C38" t="n">
+        <v>0.241487044041681</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="s">
+        <v>15</v>
+      </c>
+      <c r="B39" t="s">
+        <v>16</v>
+      </c>
+      <c r="C39" t="n">
+        <v>-0.173449227545851</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="s">
+        <v>15</v>
+      </c>
+      <c r="B40" t="s">
+        <v>16</v>
+      </c>
+      <c r="C40" t="n">
+        <v>-1.85954260146756</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="s">
+        <v>15</v>
+      </c>
+      <c r="B41" t="s">
+        <v>16</v>
+      </c>
+      <c r="C41" t="n">
+        <v>-1.05653886278028</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="s">
+        <v>15</v>
+      </c>
+      <c r="B42" t="s">
+        <v>16</v>
+      </c>
+      <c r="C42" t="n">
+        <v>-1.82559047141209</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="s">
+        <v>15</v>
+      </c>
+      <c r="B43" t="s">
+        <v>16</v>
+      </c>
+      <c r="C43" t="n">
+        <v>-0.795983337704435</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="s">
+        <v>15</v>
+      </c>
+      <c r="B44" t="s">
+        <v>16</v>
+      </c>
+      <c r="C44" t="n">
+        <v>-0.782067817678571</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="s">
+        <v>15</v>
+      </c>
+      <c r="B45" t="s">
+        <v>16</v>
+      </c>
+      <c r="C45" t="n">
+        <v>-0.206207466114767</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="s">
+        <v>15</v>
+      </c>
+      <c r="B46" t="s">
+        <v>16</v>
+      </c>
+      <c r="C46" t="n">
+        <v>-0.188596030683787</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="s">
+        <v>15</v>
+      </c>
+      <c r="B47" t="s">
+        <v>16</v>
+      </c>
+      <c r="C47" t="n">
+        <v>-1.88037226604239</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="s">
+        <v>15</v>
+      </c>
+      <c r="B48" t="s">
+        <v>16</v>
+      </c>
+      <c r="C48" t="n">
+        <v>-0.0956549121200687</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="s">
+        <v>15</v>
+      </c>
+      <c r="B49" t="s">
+        <v>16</v>
+      </c>
+      <c r="C49" t="n">
+        <v>-0.277189649387598</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="s">
+        <v>15</v>
+      </c>
+      <c r="B50" t="s">
+        <v>16</v>
+      </c>
+      <c r="C50" t="n">
+        <v>-0.086735615134315</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="s">
+        <v>15</v>
+      </c>
+      <c r="B51" t="s">
+        <v>16</v>
+      </c>
+      <c r="C51" t="n">
+        <v>-0.0523752075034043</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="s">
+        <v>15</v>
+      </c>
+      <c r="B52" t="s">
+        <v>16</v>
+      </c>
+      <c r="C52" t="n">
+        <v>-0.0549886131259674</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="s">
+        <v>15</v>
+      </c>
+      <c r="B53" t="s">
+        <v>16</v>
+      </c>
+      <c r="C53" t="n">
+        <v>-0.0618390357181771</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="s">
+        <v>15</v>
+      </c>
+      <c r="B54" t="s">
+        <v>16</v>
+      </c>
+      <c r="C54" t="n">
+        <v>-0.689749694412805</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="s">
+        <v>15</v>
+      </c>
+      <c r="B55" t="s">
+        <v>16</v>
+      </c>
+      <c r="C55" t="n">
+        <v>-1.41699809735509</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="s">
+        <v>15</v>
+      </c>
+      <c r="B56" t="s">
+        <v>16</v>
+      </c>
+      <c r="C56" t="n">
+        <v>-0.130083360928127</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="s">
+        <v>15</v>
+      </c>
+      <c r="B57" t="s">
+        <v>16</v>
+      </c>
+      <c r="C57" t="n">
+        <v>0.0826213693498952</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="s">
+        <v>15</v>
+      </c>
+      <c r="B58" t="s">
+        <v>16</v>
+      </c>
+      <c r="C58" t="n">
+        <v>-0.259230578530833</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="s">
+        <v>15</v>
+      </c>
+      <c r="B59" t="s">
+        <v>16</v>
+      </c>
+      <c r="C59" t="n">
+        <v>-0.498695481868562</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="s">
+        <v>15</v>
+      </c>
+      <c r="B60" t="s">
+        <v>16</v>
+      </c>
+      <c r="C60" t="n">
+        <v>-1.21942704975912</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="s">
+        <v>15</v>
+      </c>
+      <c r="B61" t="s">
+        <v>16</v>
+      </c>
+      <c r="C61" t="n">
+        <v>0.293541346007844</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="s">
+        <v>15</v>
+      </c>
+      <c r="B62" t="s">
+        <v>16</v>
+      </c>
+      <c r="C62" t="n">
+        <v>-0.847502541185437</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="s">
+        <v>15</v>
+      </c>
+      <c r="B63" t="s">
+        <v>16</v>
+      </c>
+      <c r="C63" t="n">
+        <v>-0.688788869689436</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="s">
+        <v>15</v>
+      </c>
+      <c r="B64" t="s">
+        <v>16</v>
+      </c>
+      <c r="C64" t="n">
+        <v>-0.053002277486065</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="s">
+        <v>15</v>
+      </c>
+      <c r="B65" t="s">
+        <v>16</v>
+      </c>
+      <c r="C65" t="n">
+        <v>0.276396147951054</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="s">
+        <v>15</v>
+      </c>
+      <c r="B66" t="s">
+        <v>16</v>
+      </c>
+      <c r="C66" t="n">
+        <v>-0.74653668818787</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="s">
+        <v>15</v>
+      </c>
+      <c r="B67" t="s">
+        <v>16</v>
+      </c>
+      <c r="C67" t="n">
+        <v>-0.0859379834359049</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="s">
+        <v>15</v>
+      </c>
+      <c r="B68" t="s">
+        <v>16</v>
+      </c>
+      <c r="C68" t="n">
+        <v>-0.68741735475476</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="s">
+        <v>15</v>
+      </c>
+      <c r="B69" t="s">
+        <v>16</v>
+      </c>
+      <c r="C69" t="n">
+        <v>-2.30123538738008</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="s">
+        <v>15</v>
+      </c>
+      <c r="B70" t="s">
+        <v>16</v>
+      </c>
+      <c r="C70" t="n">
+        <v>-0.869085034993097</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="s">
+        <v>15</v>
+      </c>
+      <c r="B71" t="s">
+        <v>16</v>
+      </c>
+      <c r="C71" t="n">
+        <v>-0.279127770919632</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="s">
+        <v>15</v>
+      </c>
+      <c r="B72" t="s">
+        <v>16</v>
+      </c>
+      <c r="C72" t="n">
+        <v>-0.982696280642532</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="s">
+        <v>15</v>
+      </c>
+      <c r="B73" t="s">
+        <v>16</v>
+      </c>
+      <c r="C73" t="n">
+        <v>-1.11734765143024</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="s">
+        <v>15</v>
+      </c>
+      <c r="B74" t="s">
+        <v>16</v>
+      </c>
+      <c r="C74" t="n">
+        <v>-0.26681789139876</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="s">
+        <v>15</v>
+      </c>
+      <c r="B75" t="s">
+        <v>16</v>
+      </c>
+      <c r="C75" t="n">
+        <v>-1.4884695500967</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="s">
+        <v>15</v>
+      </c>
+      <c r="B76" t="s">
+        <v>16</v>
+      </c>
+      <c r="C76" t="n">
+        <v>0.90566768592167</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="s">
+        <v>15</v>
+      </c>
+      <c r="B77" t="s">
+        <v>16</v>
+      </c>
+      <c r="C77" t="n">
+        <v>-1.90927396929617</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="s">
+        <v>15</v>
+      </c>
+      <c r="B78" t="s">
+        <v>16</v>
+      </c>
+      <c r="C78" t="n">
+        <v>-0.392509326028351</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="s">
+        <v>15</v>
+      </c>
+      <c r="B79" t="s">
+        <v>16</v>
+      </c>
+      <c r="C79" t="n">
+        <v>-2.260550970718</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="s">
+        <v>15</v>
+      </c>
+      <c r="B80" t="s">
+        <v>16</v>
+      </c>
+      <c r="C80" t="n">
+        <v>-0.591542902437236</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="s">
+        <v>15</v>
+      </c>
+      <c r="B81" t="s">
+        <v>16</v>
+      </c>
+      <c r="C81" t="n">
+        <v>-1.24657213717504</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="s">
+        <v>15</v>
+      </c>
+      <c r="B82" t="s">
+        <v>16</v>
+      </c>
+      <c r="C82" t="n">
+        <v>-1.49604867919015</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="s">
+        <v>15</v>
+      </c>
+      <c r="B83" t="s">
+        <v>16</v>
+      </c>
+      <c r="C83" t="n">
+        <v>-0.454425970001873</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="s">
+        <v>15</v>
+      </c>
+      <c r="B84" t="s">
+        <v>16</v>
+      </c>
+      <c r="C84" t="n">
+        <v>-0.145699721795277</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="s">
+        <v>15</v>
+      </c>
+      <c r="B85" t="s">
+        <v>16</v>
+      </c>
+      <c r="C85" t="n">
+        <v>-0.643261106595203</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="s">
+        <v>15</v>
+      </c>
+      <c r="B86" t="s">
+        <v>16</v>
+      </c>
+      <c r="C86" t="n">
+        <v>-1.06727624858159</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="s">
+        <v>15</v>
+      </c>
+      <c r="B87" t="s">
+        <v>16</v>
+      </c>
+      <c r="C87" t="n">
+        <v>-0.601590100474518</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="s">
+        <v>15</v>
+      </c>
+      <c r="B88" t="s">
+        <v>16</v>
+      </c>
+      <c r="C88" t="n">
+        <v>-0.453845710691663</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="s">
+        <v>15</v>
+      </c>
+      <c r="B89" t="s">
+        <v>16</v>
+      </c>
+      <c r="C89" t="n">
+        <v>0.031978125080434</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="s">
+        <v>15</v>
+      </c>
+      <c r="B90" t="s">
+        <v>16</v>
+      </c>
+      <c r="C90" t="n">
+        <v>-0.547541422265352</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="s">
+        <v>15</v>
+      </c>
+      <c r="B91" t="s">
+        <v>16</v>
+      </c>
+      <c r="C91" t="n">
+        <v>-1.97343141764496</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="s">
+        <v>15</v>
+      </c>
+      <c r="B92" t="s">
+        <v>16</v>
+      </c>
+      <c r="C92" t="n">
+        <v>-0.687605553444823</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="s">
+        <v>15</v>
+      </c>
+      <c r="B93" t="s">
+        <v>16</v>
+      </c>
+      <c r="C93" t="n">
+        <v>-0.158328563302979</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="s">
+        <v>15</v>
+      </c>
+      <c r="B94" t="s">
+        <v>16</v>
+      </c>
+      <c r="C94" t="n">
+        <v>-1.5560081799116</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="s">
+        <v>15</v>
+      </c>
+      <c r="B95" t="s">
+        <v>16</v>
+      </c>
+      <c r="C95" t="n">
+        <v>-0.370756493463752</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="s">
+        <v>15</v>
+      </c>
+      <c r="B96" t="s">
+        <v>16</v>
+      </c>
+      <c r="C96" t="n">
+        <v>-1.79691326245637</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="s">
+        <v>15</v>
+      </c>
+      <c r="B97" t="s">
+        <v>16</v>
+      </c>
+      <c r="C97" t="n">
+        <v>0.289566977885886</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="s">
+        <v>15</v>
+      </c>
+      <c r="B98" t="s">
+        <v>16</v>
+      </c>
+      <c r="C98" t="n">
+        <v>-1.04760216039843</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="s">
+        <v>15</v>
+      </c>
+      <c r="B99" t="s">
+        <v>16</v>
+      </c>
+      <c r="C99" t="n">
+        <v>-1.14359356381355</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="s">
+        <v>15</v>
+      </c>
+      <c r="B100" t="s">
+        <v>16</v>
+      </c>
+      <c r="C100" t="n">
+        <v>-0.508526704709394</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="s">
+        <v>15</v>
+      </c>
+      <c r="B101" t="s">
+        <v>16</v>
+      </c>
+      <c r="C101" t="n">
+        <v>-0.502368330102043</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="s">
+        <v>15</v>
+      </c>
+      <c r="B102" t="s">
+        <v>16</v>
+      </c>
+      <c r="C102" t="n">
+        <v>-1.13710645377783</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="s">
+        <v>15</v>
+      </c>
+      <c r="B103" t="s">
+        <v>16</v>
+      </c>
+      <c r="C103" t="n">
+        <v>-0.589447547201834</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="s">
+        <v>15</v>
+      </c>
+      <c r="B104" t="s">
+        <v>16</v>
+      </c>
+      <c r="C104" t="n">
+        <v>-0.317124467151922</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="s">
+        <v>15</v>
+      </c>
+      <c r="B105" t="s">
+        <v>16</v>
+      </c>
+      <c r="C105" t="n">
+        <v>-1.0213838899021</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="s">
+        <v>15</v>
+      </c>
+      <c r="B106" t="s">
+        <v>16</v>
+      </c>
+      <c r="C106" t="n">
+        <v>-1.3558674002538</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="s">
+        <v>15</v>
+      </c>
+      <c r="B107" t="s">
+        <v>16</v>
+      </c>
+      <c r="C107" t="n">
+        <v>-2.95986789730962</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="s">
+        <v>15</v>
+      </c>
+      <c r="B108" t="s">
+        <v>16</v>
+      </c>
+      <c r="C108" t="n">
+        <v>-0.0506965824965699</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="s">
+        <v>15</v>
+      </c>
+      <c r="B109" t="s">
+        <v>16</v>
+      </c>
+      <c r="C109" t="n">
+        <v>-0.0125475856717032</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="s">
+        <v>15</v>
+      </c>
+      <c r="B110" t="s">
+        <v>16</v>
+      </c>
+      <c r="C110" t="n">
+        <v>-0.307157565147546</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="s">
+        <v>15</v>
+      </c>
+      <c r="B111" t="s">
+        <v>16</v>
+      </c>
+      <c r="C111" t="n">
+        <v>-0.998245212199871</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="s">
+        <v>15</v>
+      </c>
+      <c r="B112" t="s">
+        <v>16</v>
+      </c>
+      <c r="C112" t="n">
+        <v>-0.307246454171422</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="s">
+        <v>15</v>
+      </c>
+      <c r="B113" t="s">
+        <v>16</v>
+      </c>
+      <c r="C113" t="n">
+        <v>-0.0154767493242132</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="s">
+        <v>15</v>
+      </c>
+      <c r="B114" t="s">
+        <v>16</v>
+      </c>
+      <c r="C114" t="n">
+        <v>-0.272351460498473</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="s">
+        <v>15</v>
+      </c>
+      <c r="B115" t="s">
+        <v>16</v>
+      </c>
+      <c r="C115" t="n">
+        <v>-0.137536506343952</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="s">
+        <v>15</v>
+      </c>
+      <c r="B116" t="s">
+        <v>16</v>
+      </c>
+      <c r="C116" t="n">
+        <v>-0.785435424457795</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="s">
+        <v>15</v>
+      </c>
+      <c r="B117" t="s">
+        <v>16</v>
+      </c>
+      <c r="C117" t="n">
+        <v>-0.0345469971408419</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="s">
+        <v>15</v>
+      </c>
+      <c r="B118" t="s">
+        <v>16</v>
+      </c>
+      <c r="C118" t="n">
+        <v>-0.74619929375706</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="s">
+        <v>15</v>
+      </c>
+      <c r="B119" t="s">
+        <v>16</v>
+      </c>
+      <c r="C119" t="n">
+        <v>0.438548889514501</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="s">
+        <v>15</v>
+      </c>
+      <c r="B120" t="s">
+        <v>16</v>
+      </c>
+      <c r="C120" t="n">
+        <v>-1.02574672865044</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="s">
+        <v>15</v>
+      </c>
+      <c r="B121" t="s">
+        <v>16</v>
+      </c>
+      <c r="C121" t="n">
+        <v>-0.154524587907153</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="s">
+        <v>15</v>
+      </c>
+      <c r="B122" t="s">
+        <v>16</v>
+      </c>
+      <c r="C122" t="n">
+        <v>-1.24789900122543</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="s">
+        <v>15</v>
+      </c>
+      <c r="B123" t="s">
+        <v>16</v>
+      </c>
+      <c r="C123" t="n">
+        <v>0.515737709671809</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="s">
+        <v>15</v>
+      </c>
+      <c r="B124" t="s">
+        <v>16</v>
+      </c>
+      <c r="C124" t="n">
+        <v>0.498375712735244</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="s">
+        <v>15</v>
+      </c>
+      <c r="B125" t="s">
+        <v>16</v>
+      </c>
+      <c r="C125" t="n">
+        <v>-0.720039391520215</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="s">
+        <v>15</v>
+      </c>
+      <c r="B126" t="s">
+        <v>16</v>
+      </c>
+      <c r="C126" t="n">
+        <v>-0.89384068344857</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="s">
+        <v>15</v>
+      </c>
+      <c r="B127" t="s">
+        <v>16</v>
+      </c>
+      <c r="C127" t="n">
+        <v>-2.09291663935152</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="s">
+        <v>15</v>
+      </c>
+      <c r="B128" t="s">
+        <v>16</v>
+      </c>
+      <c r="C128" t="n">
+        <v>-1.10870993583517</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="s">
+        <v>15</v>
+      </c>
+      <c r="B129" t="s">
+        <v>16</v>
+      </c>
+      <c r="C129" t="n">
+        <v>-0.745773939374828</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="s">
+        <v>15</v>
+      </c>
+      <c r="B130" t="s">
+        <v>16</v>
+      </c>
+      <c r="C130" t="n">
+        <v>-0.373025998939518</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="s">
+        <v>15</v>
+      </c>
+      <c r="B131" t="s">
+        <v>16</v>
+      </c>
+      <c r="C131" t="n">
+        <v>-0.725259843960229</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="s">
+        <v>15</v>
+      </c>
+      <c r="B132" t="s">
+        <v>16</v>
+      </c>
+      <c r="C132" t="n">
+        <v>0.0280757552757136</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="s">
+        <v>15</v>
+      </c>
+      <c r="B133" t="s">
+        <v>16</v>
+      </c>
+      <c r="C133" t="n">
+        <v>-1.4786117376062</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="s">
+        <v>15</v>
+      </c>
+      <c r="B134" t="s">
+        <v>16</v>
+      </c>
+      <c r="C134" t="n">
+        <v>0.125389480917532</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="s">
+        <v>15</v>
+      </c>
+      <c r="B135" t="s">
+        <v>16</v>
+      </c>
+      <c r="C135" t="n">
+        <v>-0.0474821732203368</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="s">
+        <v>15</v>
+      </c>
+      <c r="B136" t="s">
+        <v>16</v>
+      </c>
+      <c r="C136" t="n">
+        <v>0.168805943206304</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="s">
+        <v>15</v>
+      </c>
+      <c r="B137" t="s">
+        <v>16</v>
+      </c>
+      <c r="C137" t="n">
+        <v>-0.330833749290717</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="s">
+        <v>15</v>
+      </c>
+      <c r="B138" t="s">
+        <v>16</v>
+      </c>
+      <c r="C138" t="n">
+        <v>-1.23668500933722</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="s">
+        <v>15</v>
+      </c>
+      <c r="B139" t="s">
+        <v>16</v>
+      </c>
+      <c r="C139" t="n">
+        <v>0.15441862308506</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="s">
+        <v>15</v>
+      </c>
+      <c r="B140" t="s">
+        <v>16</v>
+      </c>
+      <c r="C140" t="n">
+        <v>-1.12057833987863</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="s">
+        <v>15</v>
+      </c>
+      <c r="B141" t="s">
+        <v>16</v>
+      </c>
+      <c r="C141" t="n">
+        <v>-0.454709174121092</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="s">
+        <v>15</v>
+      </c>
+      <c r="B142" t="s">
+        <v>16</v>
+      </c>
+      <c r="C142" t="n">
+        <v>-0.735615040284815</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="s">
+        <v>15</v>
+      </c>
+      <c r="B143" t="s">
+        <v>16</v>
+      </c>
+      <c r="C143" t="n">
+        <v>-0.203202206920817</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="s">
+        <v>15</v>
+      </c>
+      <c r="B144" t="s">
+        <v>16</v>
+      </c>
+      <c r="C144" t="n">
+        <v>-1.07386519982379</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="s">
+        <v>15</v>
+      </c>
+      <c r="B145" t="s">
+        <v>16</v>
+      </c>
+      <c r="C145" t="n">
+        <v>-0.316262770954375</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="s">
+        <v>15</v>
+      </c>
+      <c r="B146" t="s">
+        <v>16</v>
+      </c>
+      <c r="C146" t="n">
+        <v>-2.17939831785502</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="s">
+        <v>15</v>
+      </c>
+      <c r="B147" t="s">
+        <v>16</v>
+      </c>
+      <c r="C147" t="n">
+        <v>-1.04580223261268</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="s">
+        <v>15</v>
+      </c>
+      <c r="B148" t="s">
+        <v>16</v>
+      </c>
+      <c r="C148" t="n">
+        <v>-1.07581525135595</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="s">
+        <v>15</v>
+      </c>
+      <c r="B149" t="s">
+        <v>16</v>
+      </c>
+      <c r="C149" t="n">
+        <v>-0.412257056733733</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="s">
+        <v>15</v>
+      </c>
+      <c r="B150" t="s">
+        <v>16</v>
+      </c>
+      <c r="C150" t="n">
+        <v>-0.850739319239701</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="s">
+        <v>15</v>
+      </c>
+      <c r="B151" t="s">
+        <v>16</v>
+      </c>
+      <c r="C151" t="n">
+        <v>-0.527647773458769</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="s">
+        <v>15</v>
+      </c>
+      <c r="B152" t="s">
+        <v>16</v>
+      </c>
+      <c r="C152" t="n">
+        <v>-0.27556649671978</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="s">
+        <v>15</v>
+      </c>
+      <c r="B153" t="s">
+        <v>16</v>
+      </c>
+      <c r="C153" t="n">
+        <v>-0.176498521979517</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="s">
+        <v>15</v>
+      </c>
+      <c r="B154" t="s">
+        <v>16</v>
+      </c>
+      <c r="C154" t="n">
+        <v>-0.476821711969066</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="s">
+        <v>15</v>
+      </c>
+      <c r="B155" t="s">
+        <v>16</v>
+      </c>
+      <c r="C155" t="n">
+        <v>0.200031409772209</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="s">
+        <v>15</v>
+      </c>
+      <c r="B156" t="s">
+        <v>16</v>
+      </c>
+      <c r="C156" t="n">
+        <v>-0.662835564894441</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="s">
+        <v>15</v>
+      </c>
+      <c r="B157" t="s">
+        <v>16</v>
+      </c>
+      <c r="C157" t="n">
+        <v>-0.628599539770814</v>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="s">
+        <v>15</v>
+      </c>
+      <c r="B158" t="s">
+        <v>16</v>
+      </c>
+      <c r="C158" t="n">
+        <v>-1.07291519365451</v>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="s">
+        <v>15</v>
+      </c>
+      <c r="B159" t="s">
+        <v>16</v>
+      </c>
+      <c r="C159" t="n">
+        <v>-0.476724047278226</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="s">
+        <v>15</v>
+      </c>
+      <c r="B160" t="s">
+        <v>16</v>
+      </c>
+      <c r="C160" t="n">
+        <v>-0.554357285335111</v>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="s">
+        <v>15</v>
+      </c>
+      <c r="B161" t="s">
+        <v>16</v>
+      </c>
+      <c r="C161" t="n">
+        <v>-0.20691215499505</v>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="s">
+        <v>15</v>
+      </c>
+      <c r="B162" t="s">
+        <v>16</v>
+      </c>
+      <c r="C162" t="n">
+        <v>0.364390939979252</v>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="s">
+        <v>15</v>
+      </c>
+      <c r="B163" t="s">
+        <v>16</v>
+      </c>
+      <c r="C163" t="n">
+        <v>-0.590848052872437</v>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="s">
+        <v>15</v>
+      </c>
+      <c r="B164" t="s">
+        <v>16</v>
+      </c>
+      <c r="C164" t="n">
+        <v>-0.863570139411673</v>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="s">
+        <v>15</v>
+      </c>
+      <c r="B165" t="s">
+        <v>16</v>
+      </c>
+      <c r="C165" t="n">
+        <v>0.0755209398536877</v>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="s">
+        <v>15</v>
+      </c>
+      <c r="B166" t="s">
+        <v>16</v>
+      </c>
+      <c r="C166" t="n">
+        <v>-0.422381400613465</v>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="s">
+        <v>15</v>
+      </c>
+      <c r="B167" t="s">
+        <v>16</v>
+      </c>
+      <c r="C167" t="n">
+        <v>-0.531263393204263</v>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="s">
+        <v>15</v>
+      </c>
+      <c r="B168" t="s">
+        <v>16</v>
+      </c>
+      <c r="C168" t="n">
+        <v>-0.485967094175031</v>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="s">
+        <v>15</v>
+      </c>
+      <c r="B169" t="s">
+        <v>16</v>
+      </c>
+      <c r="C169" t="n">
+        <v>-0.44112018397707</v>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="s">
+        <v>15</v>
+      </c>
+      <c r="B170" t="s">
+        <v>16</v>
+      </c>
+      <c r="C170" t="n">
+        <v>-1.54304096301003</v>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="s">
+        <v>15</v>
+      </c>
+      <c r="B171" t="s">
+        <v>16</v>
+      </c>
+      <c r="C171" t="n">
+        <v>-0.146537439023041</v>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="s">
+        <v>15</v>
+      </c>
+      <c r="B172" t="s">
+        <v>16</v>
+      </c>
+      <c r="C172" t="n">
+        <v>-1.16564737525369</v>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="s">
+        <v>15</v>
+      </c>
+      <c r="B173" t="s">
+        <v>16</v>
+      </c>
+      <c r="C173" t="n">
+        <v>-0.717620671714214</v>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="s">
+        <v>15</v>
+      </c>
+      <c r="B174" t="s">
+        <v>16</v>
+      </c>
+      <c r="C174" t="n">
+        <v>-1.33148370079822</v>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="s">
+        <v>15</v>
+      </c>
+      <c r="B175" t="s">
+        <v>16</v>
+      </c>
+      <c r="C175" t="n">
+        <v>-0.523284582355004</v>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="s">
+        <v>15</v>
+      </c>
+      <c r="B176" t="s">
+        <v>16</v>
+      </c>
+      <c r="C176" t="n">
+        <v>-0.301406187885022</v>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="s">
+        <v>15</v>
+      </c>
+      <c r="B177" t="s">
+        <v>16</v>
+      </c>
+      <c r="C177" t="n">
+        <v>-0.514200252881955</v>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="s">
+        <v>15</v>
+      </c>
+      <c r="B178" t="s">
+        <v>16</v>
+      </c>
+      <c r="C178" t="n">
+        <v>-0.383659864753484</v>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="s">
+        <v>15</v>
+      </c>
+      <c r="B179" t="s">
+        <v>16</v>
+      </c>
+      <c r="C179" t="n">
+        <v>-1.00390191668842</v>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="s">
+        <v>15</v>
+      </c>
+      <c r="B180" t="s">
+        <v>16</v>
+      </c>
+      <c r="C180" t="n">
+        <v>-0.428260452249513</v>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="s">
+        <v>15</v>
+      </c>
+      <c r="B181" t="s">
+        <v>16</v>
+      </c>
+      <c r="C181" t="n">
+        <v>0.415082627561829</v>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="s">
+        <v>15</v>
+      </c>
+      <c r="B182" t="s">
+        <v>16</v>
+      </c>
+      <c r="C182" t="n">
+        <v>-0.692114622042826</v>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="s">
+        <v>15</v>
+      </c>
+      <c r="B183" t="s">
+        <v>16</v>
+      </c>
+      <c r="C183" t="n">
+        <v>-1.03675233218731</v>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="s">
+        <v>15</v>
+      </c>
+      <c r="B184" t="s">
+        <v>16</v>
+      </c>
+      <c r="C184" t="n">
+        <v>-1.59123994332057</v>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="s">
+        <v>15</v>
+      </c>
+      <c r="B185" t="s">
+        <v>16</v>
+      </c>
+      <c r="C185" t="n">
+        <v>-0.94549949790636</v>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="s">
+        <v>15</v>
+      </c>
+      <c r="B186" t="s">
+        <v>16</v>
+      </c>
+      <c r="C186" t="n">
+        <v>-1.00380134687351</v>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="s">
+        <v>15</v>
+      </c>
+      <c r="B187" t="s">
+        <v>16</v>
+      </c>
+      <c r="C187" t="n">
+        <v>-0.404043041015225</v>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="s">
+        <v>15</v>
+      </c>
+      <c r="B188" t="s">
+        <v>16</v>
+      </c>
+      <c r="C188" t="n">
+        <v>-1.07834411156126</v>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="s">
+        <v>15</v>
+      </c>
+      <c r="B189" t="s">
+        <v>16</v>
+      </c>
+      <c r="C189" t="n">
+        <v>-0.823062023952863</v>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="s">
+        <v>15</v>
+      </c>
+      <c r="B190" t="s">
+        <v>16</v>
+      </c>
+      <c r="C190" t="n">
+        <v>0.199055404214148</v>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="s">
+        <v>15</v>
+      </c>
+      <c r="B191" t="s">
+        <v>16</v>
+      </c>
+      <c r="C191" t="n">
+        <v>0.0802673655001008</v>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="s">
+        <v>15</v>
+      </c>
+      <c r="B192" t="s">
+        <v>16</v>
+      </c>
+      <c r="C192" t="n">
+        <v>-0.253767976452641</v>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="s">
+        <v>15</v>
+      </c>
+      <c r="B193" t="s">
+        <v>16</v>
+      </c>
+      <c r="C193" t="n">
+        <v>-1.47906820060478</v>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="s">
+        <v>15</v>
+      </c>
+      <c r="B194" t="s">
+        <v>16</v>
+      </c>
+      <c r="C194" t="n">
+        <v>0.226533494480953</v>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="s">
+        <v>15</v>
+      </c>
+      <c r="B195" t="s">
+        <v>16</v>
+      </c>
+      <c r="C195" t="n">
+        <v>-0.88906671465051</v>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="s">
+        <v>15</v>
+      </c>
+      <c r="B196" t="s">
+        <v>16</v>
+      </c>
+      <c r="C196" t="n">
+        <v>-0.645700412755033</v>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="s">
+        <v>15</v>
+      </c>
+      <c r="B197" t="s">
+        <v>16</v>
+      </c>
+      <c r="C197" t="n">
+        <v>-1.22705074952108</v>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="s">
+        <v>15</v>
+      </c>
+      <c r="B198" t="s">
+        <v>16</v>
+      </c>
+      <c r="C198" t="n">
+        <v>-0.312588967780915</v>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="s">
+        <v>15</v>
+      </c>
+      <c r="B199" t="s">
+        <v>16</v>
+      </c>
+      <c r="C199" t="n">
+        <v>-0.781646545076313</v>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="s">
+        <v>15</v>
+      </c>
+      <c r="B200" t="s">
+        <v>16</v>
+      </c>
+      <c r="C200" t="n">
+        <v>-0.244871492470059</v>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="s">
+        <v>15</v>
+      </c>
+      <c r="B201" t="s">
+        <v>16</v>
+      </c>
+      <c r="C201" t="n">
+        <v>-0.562983308044323</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
